--- a/GearSage-client/rate/excel/jig_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/jig_lure_detail.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="hard_lure_detail" sheetId="1" r:id="rId1"/>
+    <sheet name="jig_lure_detail" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -453,11 +457,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
+      <c r="A2" t="str">
+        <v>YYD10000</v>
+      </c>
+      <c r="B2" t="str">
+        <v>YY1000</v>
       </c>
       <c r="C2" t="str">
         <v>危牙JIG</v>
@@ -506,11 +510,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
+      <c r="A3" t="str">
+        <v>YYD10001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>YY1000</v>
       </c>
       <c r="C3" t="str">
         <v>危牙JIG</v>
@@ -559,11 +563,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
+      <c r="A4" t="str">
+        <v>YYD10002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>YY1000</v>
       </c>
       <c r="C4" t="str">
         <v>危牙JIG</v>
@@ -2188,6 +2192,18 @@
       <c r="M34" t="str">
         <v/>
       </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2229,6 +2245,18 @@
       <c r="M35" t="str">
         <v/>
       </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2270,6 +2298,18 @@
       <c r="M36" t="str">
         <v/>
       </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2311,6 +2351,18 @@
       <c r="M37" t="str">
         <v/>
       </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2352,6 +2404,18 @@
       <c r="M38" t="str">
         <v/>
       </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2393,6 +2457,18 @@
       <c r="M39" t="str">
         <v/>
       </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2434,6 +2510,18 @@
       <c r="M40" t="str">
         <v/>
       </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2475,6 +2563,18 @@
       <c r="M41" t="str">
         <v/>
       </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2516,6 +2616,18 @@
       <c r="M42" t="str">
         <v/>
       </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2557,6 +2669,18 @@
       <c r="M43" t="str">
         <v/>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2598,6 +2722,18 @@
       <c r="M44" t="str">
         <v/>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2639,6 +2775,18 @@
       <c r="M45" t="str">
         <v/>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2680,6 +2828,18 @@
       <c r="M46" t="str">
         <v/>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2721,6 +2881,18 @@
       <c r="M47" t="str">
         <v/>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2762,6 +2934,18 @@
       <c r="M48" t="str">
         <v/>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2803,6 +2987,18 @@
       <c r="M49" t="str">
         <v/>
       </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2844,6 +3040,18 @@
       <c r="M50" t="str">
         <v/>
       </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2885,6 +3093,18 @@
       <c r="M51" t="str">
         <v/>
       </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2926,6 +3146,18 @@
       <c r="M52" t="str">
         <v/>
       </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2967,6 +3199,18 @@
       <c r="M53" t="str">
         <v/>
       </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3008,6 +3252,18 @@
       <c r="M54" t="str">
         <v/>
       </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3049,6 +3305,18 @@
       <c r="M55" t="str">
         <v/>
       </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3090,6 +3358,18 @@
       <c r="M56" t="str">
         <v/>
       </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3131,6 +3411,18 @@
       <c r="M57" t="str">
         <v/>
       </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3172,6 +3464,18 @@
       <c r="M58" t="str">
         <v/>
       </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3213,6 +3517,18 @@
       <c r="M59" t="str">
         <v/>
       </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3254,6 +3570,18 @@
       <c r="M60" t="str">
         <v/>
       </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3295,6 +3623,18 @@
       <c r="M61" t="str">
         <v/>
       </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3336,6 +3676,18 @@
       <c r="M62" t="str">
         <v/>
       </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3377,6 +3729,18 @@
       <c r="M63" t="str">
         <v/>
       </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3418,6 +3782,18 @@
       <c r="M64" t="str">
         <v/>
       </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3459,6 +3835,18 @@
       <c r="M65" t="str">
         <v/>
       </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3500,6 +3888,18 @@
       <c r="M66" t="str">
         <v/>
       </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3541,6 +3941,18 @@
       <c r="M67" t="str">
         <v/>
       </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3582,6 +3994,18 @@
       <c r="M68" t="str">
         <v/>
       </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3623,6 +4047,18 @@
       <c r="M69" t="str">
         <v/>
       </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3664,6 +4100,18 @@
       <c r="M70" t="str">
         <v/>
       </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3705,6 +4153,18 @@
       <c r="M71" t="str">
         <v/>
       </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3746,6 +4206,18 @@
       <c r="M72" t="str">
         <v/>
       </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3787,6 +4259,18 @@
       <c r="M73" t="str">
         <v/>
       </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3828,6 +4312,18 @@
       <c r="M74" t="str">
         <v/>
       </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3869,6 +4365,18 @@
       <c r="M75" t="str">
         <v/>
       </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3910,6 +4418,18 @@
       <c r="M76" t="str">
         <v/>
       </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3951,6 +4471,18 @@
       <c r="M77" t="str">
         <v/>
       </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -3992,6 +4524,18 @@
       <c r="M78" t="str">
         <v/>
       </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4033,6 +4577,18 @@
       <c r="M79" t="str">
         <v/>
       </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4074,6 +4630,18 @@
       <c r="M80" t="str">
         <v/>
       </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4115,6 +4683,18 @@
       <c r="M81" t="str">
         <v/>
       </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4156,6 +4736,18 @@
       <c r="M82" t="str">
         <v/>
       </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4197,6 +4789,18 @@
       <c r="M83" t="str">
         <v/>
       </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4238,6 +4842,18 @@
       <c r="M84" t="str">
         <v/>
       </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4279,6 +4895,18 @@
       <c r="M85" t="str">
         <v/>
       </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4320,6 +4948,18 @@
       <c r="M86" t="str">
         <v/>
       </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4361,6 +5001,18 @@
       <c r="M87" t="str">
         <v/>
       </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4402,6 +5054,18 @@
       <c r="M88" t="str">
         <v/>
       </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4443,6 +5107,18 @@
       <c r="M89" t="str">
         <v/>
       </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4484,6 +5160,18 @@
       <c r="M90" t="str">
         <v/>
       </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4525,6 +5213,18 @@
       <c r="M91" t="str">
         <v/>
       </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4566,6 +5266,18 @@
       <c r="M92" t="str">
         <v/>
       </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4607,6 +5319,18 @@
       <c r="M93" t="str">
         <v/>
       </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4648,6 +5372,18 @@
       <c r="M94" t="str">
         <v/>
       </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4689,6 +5425,18 @@
       <c r="M95" t="str">
         <v/>
       </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4730,6 +5478,18 @@
       <c r="M96" t="str">
         <v/>
       </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4771,6 +5531,18 @@
       <c r="M97" t="str">
         <v/>
       </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4812,6 +5584,18 @@
       <c r="M98" t="str">
         <v/>
       </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4853,6 +5637,18 @@
       <c r="M99" t="str">
         <v/>
       </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4894,6 +5690,18 @@
       <c r="M100" t="str">
         <v/>
       </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4935,6 +5743,18 @@
       <c r="M101" t="str">
         <v/>
       </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -4976,6 +5796,18 @@
       <c r="M102" t="str">
         <v/>
       </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5017,6 +5849,18 @@
       <c r="M103" t="str">
         <v/>
       </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5058,6 +5902,18 @@
       <c r="M104" t="str">
         <v/>
       </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5099,6 +5955,18 @@
       <c r="M105" t="str">
         <v/>
       </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5140,6 +6008,18 @@
       <c r="M106" t="str">
         <v/>
       </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5181,6 +6061,18 @@
       <c r="M107" t="str">
         <v/>
       </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5222,6 +6114,18 @@
       <c r="M108" t="str">
         <v/>
       </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -5263,6 +6167,18 @@
       <c r="M109" t="str">
         <v/>
       </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -5304,6 +6220,18 @@
       <c r="M110" t="str">
         <v/>
       </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5345,6 +6273,18 @@
       <c r="M111" t="str">
         <v/>
       </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5386,6 +6326,18 @@
       <c r="M112" t="str">
         <v/>
       </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -5427,6 +6379,18 @@
       <c r="M113" t="str">
         <v/>
       </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5468,6 +6432,18 @@
       <c r="M114" t="str">
         <v/>
       </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -5509,6 +6485,18 @@
       <c r="M115" t="str">
         <v/>
       </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -5550,6 +6538,18 @@
       <c r="M116" t="str">
         <v/>
       </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -5591,6 +6591,18 @@
       <c r="M117" t="str">
         <v/>
       </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -5632,6 +6644,18 @@
       <c r="M118" t="str">
         <v/>
       </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -5673,6 +6697,18 @@
       <c r="M119" t="str">
         <v/>
       </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -5714,6 +6750,18 @@
       <c r="M120" t="str">
         <v/>
       </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -5755,6 +6803,18 @@
       <c r="M121" t="str">
         <v/>
       </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -5796,6 +6856,18 @@
       <c r="M122" t="str">
         <v/>
       </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -5837,6 +6909,18 @@
       <c r="M123" t="str">
         <v/>
       </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -5878,6 +6962,18 @@
       <c r="M124" t="str">
         <v/>
       </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -5919,6 +7015,18 @@
       <c r="M125" t="str">
         <v/>
       </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5960,6 +7068,18 @@
       <c r="M126" t="str">
         <v/>
       </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -6001,6 +7121,18 @@
       <c r="M127" t="str">
         <v/>
       </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -6042,6 +7174,18 @@
       <c r="M128" t="str">
         <v/>
       </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -6083,6 +7227,18 @@
       <c r="M129" t="str">
         <v/>
       </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -6124,6 +7280,18 @@
       <c r="M130" t="str">
         <v/>
       </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -6165,6 +7333,18 @@
       <c r="M131" t="str">
         <v/>
       </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -6206,6 +7386,18 @@
       <c r="M132" t="str">
         <v/>
       </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -6247,6 +7439,18 @@
       <c r="M133" t="str">
         <v/>
       </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -6288,6 +7492,18 @@
       <c r="M134" t="str">
         <v/>
       </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -6329,6 +7545,18 @@
       <c r="M135" t="str">
         <v/>
       </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -6370,6 +7598,18 @@
       <c r="M136" t="str">
         <v/>
       </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -6411,6 +7651,18 @@
       <c r="M137" t="str">
         <v/>
       </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -6452,6 +7704,18 @@
       <c r="M138" t="str">
         <v/>
       </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -6493,6 +7757,18 @@
       <c r="M139" t="str">
         <v/>
       </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -6534,6 +7810,18 @@
       <c r="M140" t="str">
         <v/>
       </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -6575,6 +7863,18 @@
       <c r="M141" t="str">
         <v/>
       </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -6616,6 +7916,18 @@
       <c r="M142" t="str">
         <v/>
       </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -6657,6 +7969,18 @@
       <c r="M143" t="str">
         <v/>
       </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -6698,6 +8022,18 @@
       <c r="M144" t="str">
         <v/>
       </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -6739,6 +8075,18 @@
       <c r="M145" t="str">
         <v/>
       </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -6780,6 +8128,18 @@
       <c r="M146" t="str">
         <v/>
       </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -6821,6 +8181,18 @@
       <c r="M147" t="str">
         <v/>
       </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -6862,6 +8234,18 @@
       <c r="M148" t="str">
         <v/>
       </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -6903,6 +8287,18 @@
       <c r="M149" t="str">
         <v/>
       </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -6944,6 +8340,18 @@
       <c r="M150" t="str">
         <v/>
       </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -6985,6 +8393,18 @@
       <c r="M151" t="str">
         <v/>
       </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -7026,6 +8446,18 @@
       <c r="M152" t="str">
         <v/>
       </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -7067,6 +8499,18 @@
       <c r="M153" t="str">
         <v/>
       </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -7108,6 +8552,18 @@
       <c r="M154" t="str">
         <v/>
       </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -7149,6 +8605,18 @@
       <c r="M155" t="str">
         <v/>
       </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -7190,6 +8658,18 @@
       <c r="M156" t="str">
         <v/>
       </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -7231,6 +8711,18 @@
       <c r="M157" t="str">
         <v/>
       </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -7272,6 +8764,18 @@
       <c r="M158" t="str">
         <v/>
       </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -7313,6 +8817,18 @@
       <c r="M159" t="str">
         <v/>
       </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -7354,6 +8870,18 @@
       <c r="M160" t="str">
         <v/>
       </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -7395,6 +8923,18 @@
       <c r="M161" t="str">
         <v/>
       </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -7436,6 +8976,18 @@
       <c r="M162" t="str">
         <v/>
       </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -7477,6 +9029,18 @@
       <c r="M163" t="str">
         <v/>
       </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -7518,6 +9082,18 @@
       <c r="M164" t="str">
         <v/>
       </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -7559,6 +9135,18 @@
       <c r="M165" t="str">
         <v/>
       </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -7600,6 +9188,18 @@
       <c r="M166" t="str">
         <v/>
       </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -7641,6 +9241,18 @@
       <c r="M167" t="str">
         <v/>
       </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -7682,6 +9294,18 @@
       <c r="M168" t="str">
         <v/>
       </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -7723,6 +9347,18 @@
       <c r="M169" t="str">
         <v/>
       </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -7764,6 +9400,18 @@
       <c r="M170" t="str">
         <v/>
       </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -7805,6 +9453,18 @@
       <c r="M171" t="str">
         <v/>
       </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -7846,6 +9506,18 @@
       <c r="M172" t="str">
         <v/>
       </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -7887,6 +9559,18 @@
       <c r="M173" t="str">
         <v/>
       </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -7928,6 +9612,18 @@
       <c r="M174" t="str">
         <v/>
       </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -7969,6 +9665,18 @@
       <c r="M175" t="str">
         <v/>
       </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -8010,6 +9718,18 @@
       <c r="M176" t="str">
         <v/>
       </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -8051,6 +9771,18 @@
       <c r="M177" t="str">
         <v/>
       </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -8092,6 +9824,18 @@
       <c r="M178" t="str">
         <v/>
       </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -8133,6 +9877,18 @@
       <c r="M179" t="str">
         <v/>
       </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -8174,6 +9930,18 @@
       <c r="M180" t="str">
         <v/>
       </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -8215,6 +9983,18 @@
       <c r="M181" t="str">
         <v/>
       </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -8256,6 +10036,18 @@
       <c r="M182" t="str">
         <v/>
       </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -8297,6 +10089,18 @@
       <c r="M183" t="str">
         <v/>
       </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -8338,6 +10142,18 @@
       <c r="M184" t="str">
         <v/>
       </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -8379,6 +10195,18 @@
       <c r="M185" t="str">
         <v/>
       </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -8420,6 +10248,18 @@
       <c r="M186" t="str">
         <v/>
       </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -8461,6 +10301,18 @@
       <c r="M187" t="str">
         <v/>
       </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -8502,6 +10354,18 @@
       <c r="M188" t="str">
         <v/>
       </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -8543,6 +10407,18 @@
       <c r="M189" t="str">
         <v/>
       </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -8584,6 +10460,18 @@
       <c r="M190" t="str">
         <v/>
       </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -8625,6 +10513,18 @@
       <c r="M191" t="str">
         <v/>
       </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -8666,6 +10566,18 @@
       <c r="M192" t="str">
         <v/>
       </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -8707,6 +10619,18 @@
       <c r="M193" t="str">
         <v/>
       </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -8748,6 +10672,18 @@
       <c r="M194" t="str">
         <v/>
       </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -8789,6 +10725,18 @@
       <c r="M195" t="str">
         <v/>
       </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -8830,6 +10778,18 @@
       <c r="M196" t="str">
         <v/>
       </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -8871,6 +10831,18 @@
       <c r="M197" t="str">
         <v/>
       </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -8912,6 +10884,18 @@
       <c r="M198" t="str">
         <v/>
       </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -8953,6 +10937,18 @@
       <c r="M199" t="str">
         <v/>
       </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -8994,6 +10990,18 @@
       <c r="M200" t="str">
         <v/>
       </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -9035,6 +11043,18 @@
       <c r="M201" t="str">
         <v/>
       </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -9076,6 +11096,18 @@
       <c r="M202" t="str">
         <v/>
       </c>
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -9117,6 +11149,18 @@
       <c r="M203" t="str">
         <v/>
       </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -9158,6 +11202,18 @@
       <c r="M204" t="str">
         <v/>
       </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -9199,6 +11255,18 @@
       <c r="M205" t="str">
         <v/>
       </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -9240,6 +11308,18 @@
       <c r="M206" t="str">
         <v/>
       </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -9281,6 +11361,18 @@
       <c r="M207" t="str">
         <v/>
       </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -9322,6 +11414,18 @@
       <c r="M208" t="str">
         <v/>
       </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -9363,6 +11467,18 @@
       <c r="M209" t="str">
         <v/>
       </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -9404,6 +11520,18 @@
       <c r="M210" t="str">
         <v/>
       </c>
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v/>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -9445,6 +11573,18 @@
       <c r="M211" t="str">
         <v/>
       </c>
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -9486,6 +11626,18 @@
       <c r="M212" t="str">
         <v/>
       </c>
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" t="str">
+        <v/>
+      </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -9527,6 +11679,18 @@
       <c r="M213" t="str">
         <v/>
       </c>
+      <c r="N213" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
+        <v/>
+      </c>
+      <c r="P213" t="str">
+        <v/>
+      </c>
+      <c r="Q213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -9568,6 +11732,18 @@
       <c r="M214" t="str">
         <v/>
       </c>
+      <c r="N214" t="str">
+        <v/>
+      </c>
+      <c r="O214" t="str">
+        <v/>
+      </c>
+      <c r="P214" t="str">
+        <v/>
+      </c>
+      <c r="Q214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -9609,6 +11785,18 @@
       <c r="M215" t="str">
         <v/>
       </c>
+      <c r="N215" t="str">
+        <v/>
+      </c>
+      <c r="O215" t="str">
+        <v/>
+      </c>
+      <c r="P215" t="str">
+        <v/>
+      </c>
+      <c r="Q215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -9650,6 +11838,18 @@
       <c r="M216" t="str">
         <v/>
       </c>
+      <c r="N216" t="str">
+        <v/>
+      </c>
+      <c r="O216" t="str">
+        <v/>
+      </c>
+      <c r="P216" t="str">
+        <v/>
+      </c>
+      <c r="Q216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -9691,6 +11891,18 @@
       <c r="M217" t="str">
         <v/>
       </c>
+      <c r="N217" t="str">
+        <v/>
+      </c>
+      <c r="O217" t="str">
+        <v/>
+      </c>
+      <c r="P217" t="str">
+        <v/>
+      </c>
+      <c r="Q217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -9732,6 +11944,18 @@
       <c r="M218" t="str">
         <v/>
       </c>
+      <c r="N218" t="str">
+        <v/>
+      </c>
+      <c r="O218" t="str">
+        <v/>
+      </c>
+      <c r="P218" t="str">
+        <v/>
+      </c>
+      <c r="Q218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -9773,6 +11997,18 @@
       <c r="M219" t="str">
         <v/>
       </c>
+      <c r="N219" t="str">
+        <v/>
+      </c>
+      <c r="O219" t="str">
+        <v/>
+      </c>
+      <c r="P219" t="str">
+        <v/>
+      </c>
+      <c r="Q219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -9814,6 +12050,18 @@
       <c r="M220" t="str">
         <v/>
       </c>
+      <c r="N220" t="str">
+        <v/>
+      </c>
+      <c r="O220" t="str">
+        <v/>
+      </c>
+      <c r="P220" t="str">
+        <v/>
+      </c>
+      <c r="Q220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -9855,6 +12103,18 @@
       <c r="M221" t="str">
         <v/>
       </c>
+      <c r="N221" t="str">
+        <v/>
+      </c>
+      <c r="O221" t="str">
+        <v/>
+      </c>
+      <c r="P221" t="str">
+        <v/>
+      </c>
+      <c r="Q221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -9896,6 +12156,18 @@
       <c r="M222" t="str">
         <v/>
       </c>
+      <c r="N222" t="str">
+        <v/>
+      </c>
+      <c r="O222" t="str">
+        <v/>
+      </c>
+      <c r="P222" t="str">
+        <v/>
+      </c>
+      <c r="Q222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -9937,6 +12209,18 @@
       <c r="M223" t="str">
         <v/>
       </c>
+      <c r="N223" t="str">
+        <v/>
+      </c>
+      <c r="O223" t="str">
+        <v/>
+      </c>
+      <c r="P223" t="str">
+        <v/>
+      </c>
+      <c r="Q223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -9978,6 +12262,18 @@
       <c r="M224" t="str">
         <v/>
       </c>
+      <c r="N224" t="str">
+        <v/>
+      </c>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+      <c r="P224" t="str">
+        <v/>
+      </c>
+      <c r="Q224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -10019,6 +12315,18 @@
       <c r="M225" t="str">
         <v/>
       </c>
+      <c r="N225" t="str">
+        <v/>
+      </c>
+      <c r="O225" t="str">
+        <v/>
+      </c>
+      <c r="P225" t="str">
+        <v/>
+      </c>
+      <c r="Q225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -10060,6 +12368,18 @@
       <c r="M226" t="str">
         <v/>
       </c>
+      <c r="N226" t="str">
+        <v/>
+      </c>
+      <c r="O226" t="str">
+        <v/>
+      </c>
+      <c r="P226" t="str">
+        <v/>
+      </c>
+      <c r="Q226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -10101,6 +12421,18 @@
       <c r="M227" t="str">
         <v/>
       </c>
+      <c r="N227" t="str">
+        <v/>
+      </c>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+      <c r="P227" t="str">
+        <v/>
+      </c>
+      <c r="Q227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -10142,6 +12474,18 @@
       <c r="M228" t="str">
         <v/>
       </c>
+      <c r="N228" t="str">
+        <v/>
+      </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v/>
+      </c>
+      <c r="Q228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -10183,6 +12527,18 @@
       <c r="M229" t="str">
         <v/>
       </c>
+      <c r="N229" t="str">
+        <v/>
+      </c>
+      <c r="O229" t="str">
+        <v/>
+      </c>
+      <c r="P229" t="str">
+        <v/>
+      </c>
+      <c r="Q229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -10224,6 +12580,18 @@
       <c r="M230" t="str">
         <v/>
       </c>
+      <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
+      <c r="Q230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -10265,6 +12633,18 @@
       <c r="M231" t="str">
         <v/>
       </c>
+      <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
+      <c r="P231" t="str">
+        <v/>
+      </c>
+      <c r="Q231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -10306,6 +12686,18 @@
       <c r="M232" t="str">
         <v/>
       </c>
+      <c r="N232" t="str">
+        <v/>
+      </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+      <c r="P232" t="str">
+        <v/>
+      </c>
+      <c r="Q232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -10345,6 +12737,18 @@
         <v>4550133505904</v>
       </c>
       <c r="M233" t="str">
+        <v/>
+      </c>
+      <c r="N233" t="str">
+        <v/>
+      </c>
+      <c r="O233" t="str">
+        <v/>
+      </c>
+      <c r="P233" t="str">
+        <v/>
+      </c>
+      <c r="Q233" t="str">
         <v/>
       </c>
     </row>

--- a/GearSage-client/rate/excel/jig_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/jig_lure_detail.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">

--- a/GearSage-client/rate/excel/jig_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/jig_lure_detail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q233"/>
+  <dimension ref="A1:Q243"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12748,9 +12748,539 @@
         <v/>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>KLD10023</v>
+      </c>
+      <c r="B234" t="str">
+        <v>KL1023</v>
+      </c>
+      <c r="C234" t="str">
+        <v>ランブレードジグ</v>
+      </c>
+      <c r="D234" t="str">
+        <v/>
+      </c>
+      <c r="E234" t="str">
+        <v/>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v>2026-04-10T05:01:42.781Z</v>
+      </c>
+      <c r="J234" t="str">
+        <v>2026-04-10T05:01:42.781Z</v>
+      </c>
+      <c r="K234" t="str">
+        <v/>
+      </c>
+      <c r="L234" t="str">
+        <v/>
+      </c>
+      <c r="M234" t="str">
+        <v/>
+      </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <v/>
+      </c>
+      <c r="Q234" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>KLD10024</v>
+      </c>
+      <c r="B235" t="str">
+        <v>KL1024</v>
+      </c>
+      <c r="C235" t="str">
+        <v>キャスティングジグ</v>
+      </c>
+      <c r="D235" t="str">
+        <v/>
+      </c>
+      <c r="E235" t="str">
+        <v/>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <v/>
+      </c>
+      <c r="I235" t="str">
+        <v>2026-04-10T05:01:44.227Z</v>
+      </c>
+      <c r="J235" t="str">
+        <v>2026-04-10T05:01:44.227Z</v>
+      </c>
+      <c r="K235" t="str">
+        <v/>
+      </c>
+      <c r="L235" t="str">
+        <v/>
+      </c>
+      <c r="M235" t="str">
+        <v/>
+      </c>
+      <c r="N235" t="str">
+        <v/>
+      </c>
+      <c r="O235" t="str">
+        <v/>
+      </c>
+      <c r="P235" t="str">
+        <v/>
+      </c>
+      <c r="Q235" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>KLD10025</v>
+      </c>
+      <c r="B236" t="str">
+        <v>KL1025</v>
+      </c>
+      <c r="C236" t="str">
+        <v>スイングスイマー</v>
+      </c>
+      <c r="D236" t="str">
+        <v/>
+      </c>
+      <c r="E236" t="str">
+        <v/>
+      </c>
+      <c r="F236" t="str">
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <v>2026-04-10T05:01:45.770Z</v>
+      </c>
+      <c r="J236" t="str">
+        <v>2026-04-10T05:01:45.770Z</v>
+      </c>
+      <c r="K236" t="str">
+        <v/>
+      </c>
+      <c r="L236" t="str">
+        <v/>
+      </c>
+      <c r="M236" t="str">
+        <v/>
+      </c>
+      <c r="N236" t="str">
+        <v/>
+      </c>
+      <c r="O236" t="str">
+        <v/>
+      </c>
+      <c r="P236" t="str">
+        <v/>
+      </c>
+      <c r="Q236" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>KLD10026</v>
+      </c>
+      <c r="B237" t="str">
+        <v>KL1026</v>
+      </c>
+      <c r="C237" t="str">
+        <v>クランキンフットボールジグ</v>
+      </c>
+      <c r="D237" t="str">
+        <v/>
+      </c>
+      <c r="E237" t="str">
+        <v/>
+      </c>
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <v>2026-04-10T05:01:47.045Z</v>
+      </c>
+      <c r="J237" t="str">
+        <v>2026-04-10T05:01:47.045Z</v>
+      </c>
+      <c r="K237" t="str">
+        <v/>
+      </c>
+      <c r="L237" t="str">
+        <v/>
+      </c>
+      <c r="M237" t="str">
+        <v/>
+      </c>
+      <c r="N237" t="str">
+        <v/>
+      </c>
+      <c r="O237" t="str">
+        <v/>
+      </c>
+      <c r="P237" t="str">
+        <v/>
+      </c>
+      <c r="Q237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>KLD10027</v>
+      </c>
+      <c r="B238" t="str">
+        <v>KL1027</v>
+      </c>
+      <c r="C238" t="str">
+        <v>ラバージグ モデル Ⅰ Ver.2.0</v>
+      </c>
+      <c r="D238" t="str">
+        <v/>
+      </c>
+      <c r="E238" t="str">
+        <v/>
+      </c>
+      <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <v>2026-04-10T05:01:48.745Z</v>
+      </c>
+      <c r="J238" t="str">
+        <v>2026-04-10T05:01:48.745Z</v>
+      </c>
+      <c r="K238" t="str">
+        <v/>
+      </c>
+      <c r="L238" t="str">
+        <v/>
+      </c>
+      <c r="M238" t="str">
+        <v/>
+      </c>
+      <c r="N238" t="str">
+        <v/>
+      </c>
+      <c r="O238" t="str">
+        <v/>
+      </c>
+      <c r="P238" t="str">
+        <v/>
+      </c>
+      <c r="Q238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>KLD10028</v>
+      </c>
+      <c r="B239" t="str">
+        <v>KL1028</v>
+      </c>
+      <c r="C239" t="str">
+        <v>ラバージグ モデル Ⅳ ヘビーデューティージグ</v>
+      </c>
+      <c r="D239" t="str">
+        <v/>
+      </c>
+      <c r="E239" t="str">
+        <v/>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+      <c r="H239" t="str">
+        <v/>
+      </c>
+      <c r="I239" t="str">
+        <v>2026-04-10T05:01:50.828Z</v>
+      </c>
+      <c r="J239" t="str">
+        <v>2026-04-10T05:01:50.828Z</v>
+      </c>
+      <c r="K239" t="str">
+        <v/>
+      </c>
+      <c r="L239" t="str">
+        <v/>
+      </c>
+      <c r="M239" t="str">
+        <v/>
+      </c>
+      <c r="N239" t="str">
+        <v/>
+      </c>
+      <c r="O239" t="str">
+        <v/>
+      </c>
+      <c r="P239" t="str">
+        <v/>
+      </c>
+      <c r="Q239" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>KLD10029</v>
+      </c>
+      <c r="B240" t="str">
+        <v>KL1029</v>
+      </c>
+      <c r="C240" t="str">
+        <v>タングステンラバージグ モデル II Ver. 2.0</v>
+      </c>
+      <c r="D240" t="str">
+        <v/>
+      </c>
+      <c r="E240" t="str">
+        <v/>
+      </c>
+      <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <v>2026-04-10T05:01:52.477Z</v>
+      </c>
+      <c r="J240" t="str">
+        <v>2026-04-10T05:01:52.477Z</v>
+      </c>
+      <c r="K240" t="str">
+        <v/>
+      </c>
+      <c r="L240" t="str">
+        <v/>
+      </c>
+      <c r="M240" t="str">
+        <v/>
+      </c>
+      <c r="N240" t="str">
+        <v/>
+      </c>
+      <c r="O240" t="str">
+        <v/>
+      </c>
+      <c r="P240" t="str">
+        <v/>
+      </c>
+      <c r="Q240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>KLD10030</v>
+      </c>
+      <c r="B241" t="str">
+        <v>KL1030</v>
+      </c>
+      <c r="C241" t="str">
+        <v>モデルIII スイムジグ</v>
+      </c>
+      <c r="D241" t="str">
+        <v/>
+      </c>
+      <c r="E241" t="str">
+        <v/>
+      </c>
+      <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <v>2026-04-10T05:01:55.893Z</v>
+      </c>
+      <c r="J241" t="str">
+        <v>2026-04-10T05:01:55.893Z</v>
+      </c>
+      <c r="K241" t="str">
+        <v/>
+      </c>
+      <c r="L241" t="str">
+        <v/>
+      </c>
+      <c r="M241" t="str">
+        <v/>
+      </c>
+      <c r="N241" t="str">
+        <v/>
+      </c>
+      <c r="O241" t="str">
+        <v/>
+      </c>
+      <c r="P241" t="str">
+        <v/>
+      </c>
+      <c r="Q241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>KLD10031</v>
+      </c>
+      <c r="B242" t="str">
+        <v>KL1031</v>
+      </c>
+      <c r="C242" t="str">
+        <v>ガードスピンジグ</v>
+      </c>
+      <c r="D242" t="str">
+        <v/>
+      </c>
+      <c r="E242" t="str">
+        <v/>
+      </c>
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <v>2026-04-10T05:01:57.179Z</v>
+      </c>
+      <c r="J242" t="str">
+        <v>2026-04-10T05:01:57.179Z</v>
+      </c>
+      <c r="K242" t="str">
+        <v/>
+      </c>
+      <c r="L242" t="str">
+        <v/>
+      </c>
+      <c r="M242" t="str">
+        <v/>
+      </c>
+      <c r="N242" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
+      <c r="P242" t="str">
+        <v/>
+      </c>
+      <c r="Q242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>KLD10032</v>
+      </c>
+      <c r="B243" t="str">
+        <v>KL1032</v>
+      </c>
+      <c r="C243" t="str">
+        <v>モノスピンジグ</v>
+      </c>
+      <c r="D243" t="str">
+        <v/>
+      </c>
+      <c r="E243" t="str">
+        <v/>
+      </c>
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v>2026-04-10T05:01:58.540Z</v>
+      </c>
+      <c r="J243" t="str">
+        <v>2026-04-10T05:01:58.540Z</v>
+      </c>
+      <c r="K243" t="str">
+        <v/>
+      </c>
+      <c r="L243" t="str">
+        <v/>
+      </c>
+      <c r="M243" t="str">
+        <v/>
+      </c>
+      <c r="N243" t="str">
+        <v/>
+      </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
+      <c r="P243" t="str">
+        <v/>
+      </c>
+      <c r="Q243" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q233"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q243"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/jig_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/jig_lure_detail.xlsx
@@ -12750,22 +12750,22 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>KLD10023</v>
+        <v>KLD10073</v>
       </c>
       <c r="B234" t="str">
         <v>KL1023</v>
       </c>
       <c r="C234" t="str">
-        <v>ランブレードジグ</v>
+        <v>ウエイトは3サイズウエイトラインナップは3/8、1/2、5/8oz の3サイズをご用意しております</v>
       </c>
       <c r="D234" t="str">
-        <v/>
+        <v>5/8oz</v>
       </c>
       <c r="E234" t="str">
         <v/>
       </c>
       <c r="F234" t="str">
-        <v/>
+        <v>ウエイトは3サイズウエイトラインナップは3/8、1/2、5/8oz の3サイズをご用意しております</v>
       </c>
       <c r="G234" t="str">
         <v/>
@@ -12774,10 +12774,10 @@
         <v/>
       </c>
       <c r="I234" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="K234" t="str">
         <v/>
@@ -12803,7 +12803,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>KLD10024</v>
+        <v>KLD10074</v>
       </c>
       <c r="B235" t="str">
         <v>KL1024</v>
@@ -12827,10 +12827,10 @@
         <v/>
       </c>
       <c r="I235" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="K235" t="str">
         <v/>
@@ -12856,7 +12856,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>KLD10025</v>
+        <v>KLD10075</v>
       </c>
       <c r="B236" t="str">
         <v>KL1025</v>
@@ -12880,10 +12880,10 @@
         <v/>
       </c>
       <c r="I236" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="K236" t="str">
         <v/>
@@ -12909,7 +12909,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>KLD10026</v>
+        <v>KLD10076</v>
       </c>
       <c r="B237" t="str">
         <v>KL1026</v>
@@ -12933,10 +12933,10 @@
         <v/>
       </c>
       <c r="I237" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="K237" t="str">
         <v/>
@@ -12962,7 +12962,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>KLD10027</v>
+        <v>KLD10077</v>
       </c>
       <c r="B238" t="str">
         <v>KL1027</v>
@@ -12986,10 +12986,10 @@
         <v/>
       </c>
       <c r="I238" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="K238" t="str">
         <v/>
@@ -13015,22 +13015,22 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>KLD10028</v>
+        <v>KLD10078</v>
       </c>
       <c r="B239" t="str">
         <v>KL1028</v>
       </c>
       <c r="C239" t="str">
-        <v>ラバージグ モデル Ⅳ ヘビーデューティージグ</v>
+        <v>パワーゲームに必要な3サイズ</v>
       </c>
       <c r="D239" t="str">
-        <v/>
+        <v>1oz</v>
       </c>
       <c r="E239" t="str">
         <v/>
       </c>
       <c r="F239" t="str">
-        <v/>
+        <v>パワーゲームに必要な3サイズ</v>
       </c>
       <c r="G239" t="str">
         <v/>
@@ -13039,10 +13039,10 @@
         <v/>
       </c>
       <c r="I239" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="K239" t="str">
         <v/>
@@ -13068,7 +13068,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>KLD10029</v>
+        <v>KLD10079</v>
       </c>
       <c r="B240" t="str">
         <v>KL1029</v>
@@ -13092,10 +13092,10 @@
         <v/>
       </c>
       <c r="I240" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="K240" t="str">
         <v/>
@@ -13121,7 +13121,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>KLD10030</v>
+        <v>KLD10080</v>
       </c>
       <c r="B241" t="str">
         <v>KL1030</v>
@@ -13145,10 +13145,10 @@
         <v/>
       </c>
       <c r="I241" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="K241" t="str">
         <v/>
@@ -13174,7 +13174,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>KLD10031</v>
+        <v>KLD10081</v>
       </c>
       <c r="B242" t="str">
         <v>KL1031</v>
@@ -13198,10 +13198,10 @@
         <v/>
       </c>
       <c r="I242" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="K242" t="str">
         <v/>
@@ -13227,7 +13227,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>KLD10032</v>
+        <v>KLD10082</v>
       </c>
       <c r="B243" t="str">
         <v>KL1032</v>
@@ -13251,10 +13251,10 @@
         <v/>
       </c>
       <c r="I243" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="K243" t="str">
         <v/>

--- a/GearSage-client/rate/excel/jig_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/jig_lure_detail.xlsx
@@ -613,16 +613,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>MLD11695</v>
+        <v>DLD10557</v>
       </c>
       <c r="B5" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C5" t="str">
-        <v>MAGDRAFT HEAD ＃5/0 1/4oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　グ　リーンパンプキンブルーフレーク</v>
       </c>
       <c r="D5" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -643,10 +643,10 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>＃5/0 1/4oz.</v>
+        <v>リーンパンプキンブルーフレーク</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>4550133464065</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -666,16 +666,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MLD11696</v>
+        <v>DLD10558</v>
       </c>
       <c r="B6" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C6" t="str">
-        <v>MAGDRAFT HEAD ＃5/0 3/8oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　チラシ</v>
       </c>
       <c r="D6" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -687,7 +687,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -696,10 +696,10 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>＃5/0 3/8oz.</v>
+        <v>チラシ</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>4550133464072</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -719,16 +719,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MLD11697</v>
+        <v>DLD10559</v>
       </c>
       <c r="B7" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C7" t="str">
-        <v>MAGDRAFT HEAD ＃5/0 1/2oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　スジエビ</v>
       </c>
       <c r="D7" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -740,7 +740,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -749,10 +749,10 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>＃5/0 1/2oz.</v>
+        <v>スジエビ</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>4550133464089</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -772,16 +772,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MLD11698</v>
+        <v>DLD10560</v>
       </c>
       <c r="B8" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C8" t="str">
-        <v>MAGDRAFT HEAD ＃5/0 5/8oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　ヌマザリ</v>
       </c>
       <c r="D8" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -802,10 +802,10 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>＃5/0 5/8oz.</v>
+        <v>ヌマザリ</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>4550133464096</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -825,16 +825,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MLD11699</v>
+        <v>DLD10561</v>
       </c>
       <c r="B9" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C9" t="str">
-        <v>MAGDRAFT HEAD ＃5/0 3/4oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　サマークロー</v>
       </c>
       <c r="D9" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -855,10 +855,10 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>＃5/0 3/4oz.</v>
+        <v>サマークロー</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>4550133464102</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -878,16 +878,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>MLD11700</v>
+        <v>DLD10562</v>
       </c>
       <c r="B10" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C10" t="str">
-        <v>MAGDRAFT HEAD ＃6/0 3/8oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　シナモンブルーフレーク</v>
       </c>
       <c r="D10" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -899,7 +899,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -908,10 +908,10 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>＃6/0 3/8oz.</v>
+        <v>シナモンブルーフレーク</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>4550133464119</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -931,16 +931,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>MLD11701</v>
+        <v>DLD10563</v>
       </c>
       <c r="B11" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C11" t="str">
-        <v>MAGDRAFT HEAD ＃6/0 1/2oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　テナガピンク</v>
       </c>
       <c r="D11" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -952,7 +952,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -961,10 +961,10 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>＃6/0 1/2oz.</v>
+        <v>テナガピンク</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>4550133464126</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -984,16 +984,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>MLD11702</v>
+        <v>DLD10564</v>
       </c>
       <c r="B12" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C12" t="str">
-        <v>MAGDRAFT HEAD ＃6/0 5/8oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　パールスモーク</v>
       </c>
       <c r="D12" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>2.7</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -1005,7 +1005,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -1014,10 +1014,10 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>＃6/0 5/8oz.</v>
+        <v>パールスモーク</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>4550133464133</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -1037,16 +1037,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>MLD11703</v>
+        <v>DLD10565</v>
       </c>
       <c r="B13" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C13" t="str">
-        <v>MAGDRAFT HEAD ＃6/0 3/4oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　グ　リーンパンプキンブルーフレーク</v>
       </c>
       <c r="D13" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -1058,7 +1058,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -1067,10 +1067,10 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>＃6/0 3/4oz.</v>
+        <v>リーンパンプキンブルーフレーク</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>4550133464140</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -1090,16 +1090,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MLD11704</v>
+        <v>DLD10566</v>
       </c>
       <c r="B14" t="str">
-        <v>ML1131</v>
+        <v>DL1056</v>
       </c>
       <c r="C14" t="str">
-        <v>MAGDRAFT HEAD ＃6/0 1oz.</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　チラシ</v>
       </c>
       <c r="D14" t="str">
-        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -1111,7 +1111,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
+        <v>650</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1120,10 +1120,10 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>＃6/0 1oz.</v>
+        <v>チラシ</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>4550133464157</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -1143,16 +1143,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MLD11715</v>
+        <v>DLD10567</v>
       </c>
       <c r="B15" t="str">
-        <v>ML1133</v>
+        <v>DL1056</v>
       </c>
       <c r="C15" t="str">
-        <v>OKASHIRA SCREW HEAD</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　スジエビ</v>
       </c>
       <c r="D15" t="str">
-        <v>＃2/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃3/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃4/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -1164,7 +1164,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>650</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>スジエビ</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>4550133464164</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1196,16 +1196,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>MLD11716</v>
+        <v>DLD10568</v>
       </c>
       <c r="B16" t="str">
-        <v>ML1134</v>
+        <v>DL1056</v>
       </c>
       <c r="C16" t="str">
-        <v>OKASHIRA HEAD</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　ヌマザリ</v>
       </c>
       <c r="D16" t="str">
-        <v>＃2/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃3/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃4/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>650</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -1226,10 +1226,10 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>ヌマザリ</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>4550133464171</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1249,16 +1249,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>MLD11717</v>
+        <v>DLD10569</v>
       </c>
       <c r="B17" t="str">
-        <v>ML1135</v>
+        <v>DL1056</v>
       </c>
       <c r="C17" t="str">
-        <v>OKASHIRA HEAD-HG（Huge-Contact）</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　サマークロー</v>
       </c>
       <c r="D17" t="str">
-        <v>＃2/0：3/8oz., 1/2oz., 5/8oz.＃3/0：3/8oz., 1/2oz., 5/8oz.＃4/0：1/2oz., 3/8oz., 3/4oz.＃5/0：1/2oz., 3/8oz., 3/4oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1270,7 +1270,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>650</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1279,10 +1279,10 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>サマークロー</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>4550133464188</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1302,16 +1302,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>MLD11718</v>
+        <v>DLD10570</v>
       </c>
       <c r="B18" t="str">
-        <v>ML1136</v>
+        <v>DL1056</v>
       </c>
       <c r="C18" t="str">
-        <v>ROBIN BLADE B BLUE</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　シナモンブルーフレーク</v>
       </c>
       <c r="D18" t="str">
-        <v>3/8oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1323,7 +1323,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>メーカー希望小売価格（税別）1,150 円</v>
+        <v>650</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1332,10 +1332,10 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>B BLUE</v>
+        <v>シナモンブルーフレーク</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>4550133464195</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1355,16 +1355,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>MLD11719</v>
+        <v>DLD10571</v>
       </c>
       <c r="B19" t="str">
-        <v>ML1136</v>
+        <v>DL1056</v>
       </c>
       <c r="C19" t="str">
-        <v>ROBIN BLADE VARRACUDA HASU</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　テナガピンク</v>
       </c>
       <c r="D19" t="str">
-        <v>3/8oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1376,7 +1376,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>メーカー希望小売価格（税別）1,150 円</v>
+        <v>650</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1385,10 +1385,10 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>VARRACUDA HASU</v>
+        <v>テナガピンク</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>4550133464201</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1408,16 +1408,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>MLD11720</v>
+        <v>DLD10572</v>
       </c>
       <c r="B20" t="str">
-        <v>ML1136</v>
+        <v>DL1056</v>
       </c>
       <c r="C20" t="str">
-        <v>ROBIN BLADE TOWER BLIDGE WAKASAGI</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　パールスモーク</v>
       </c>
       <c r="D20" t="str">
-        <v>3/8oz.</v>
+        <v>3.5</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1429,7 +1429,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>メーカー希望小売価格（税別）1,150 円</v>
+        <v>650</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1438,10 +1438,10 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>TOWER BLIDGE WAKASAGI</v>
+        <v>パールスモーク</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>4550133464218</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1461,16 +1461,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>MLD11721</v>
+        <v>DLD10573</v>
       </c>
       <c r="B21" t="str">
-        <v>ML1136</v>
+        <v>DL1056</v>
       </c>
       <c r="C21" t="str">
-        <v>ROBIN BLADE WARS GILL</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　グ　リーンパンプキンブルーフレーク</v>
       </c>
       <c r="D21" t="str">
-        <v>3/8oz.</v>
+        <v>4.7</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1482,7 +1482,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>メーカー希望小売価格（税別）1,150 円</v>
+        <v>650</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1491,10 +1491,10 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>WARS GILL</v>
+        <v>リーンパンプキンブルーフレーク</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>4550133464225</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>MLD11722</v>
+        <v>DLD10574</v>
       </c>
       <c r="B22" t="str">
-        <v>ML1136</v>
+        <v>DL1056</v>
       </c>
       <c r="C22" t="str">
-        <v>ROBIN BLADE ANOARO GILL</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　チラシ</v>
       </c>
       <c r="D22" t="str">
-        <v>3/8oz.</v>
+        <v>4.7</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>メーカー希望小売価格（税別）1,150 円</v>
+        <v>650</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1544,10 +1544,10 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>ANOARO GILL</v>
+        <v>チラシ</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>4550133464232</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1567,16 +1567,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>MLD11723</v>
+        <v>DLD10575</v>
       </c>
       <c r="B23" t="str">
-        <v>ML1136</v>
+        <v>DL1056</v>
       </c>
       <c r="C23" t="str">
-        <v>ROBIN BLADE CHART DRIVER</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　スジエビ</v>
       </c>
       <c r="D23" t="str">
-        <v>3/8oz.</v>
+        <v>4.7</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1588,7 +1588,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>メーカー希望小売価格（税別）1,150 円</v>
+        <v>650</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1597,10 +1597,10 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>CHART DRIVER</v>
+        <v>スジエビ</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>4550133464249</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1620,16 +1620,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MLD11734</v>
+        <v>DLD10576</v>
       </c>
       <c r="B24" t="str">
-        <v>ML1138</v>
+        <v>DL1056</v>
       </c>
       <c r="C24" t="str">
-        <v>UOZE SWIMMER HASU</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　ヌマザリ</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1641,7 +1641,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>650</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1650,13 +1650,13 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>HASU</v>
+        <v>ヌマザリ</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>4550133464256</v>
       </c>
       <c r="M24" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,16 +1673,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MLD11735</v>
+        <v>DLD10577</v>
       </c>
       <c r="B25" t="str">
-        <v>ML1138</v>
+        <v>DL1056</v>
       </c>
       <c r="C25" t="str">
-        <v>UOZE SWIMMER AYU</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　サマークロー</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1694,7 +1694,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>650</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1703,13 +1703,13 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>AYU</v>
+        <v>サマークロー</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>4550133464263</v>
       </c>
       <c r="M25" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,16 +1726,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MLD11736</v>
+        <v>DLD10578</v>
       </c>
       <c r="B26" t="str">
-        <v>ML1138</v>
+        <v>DL1056</v>
       </c>
       <c r="C26" t="str">
-        <v>UOZE SWIMMER WAKASAGI</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　シナモンブルーフレーク</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1747,7 +1747,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>650</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1756,13 +1756,13 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>WAKASAGI</v>
+        <v>シナモンブルーフレーク</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>4550133464270</v>
       </c>
       <c r="M26" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,16 +1779,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>MLD11737</v>
+        <v>DLD10579</v>
       </c>
       <c r="B27" t="str">
-        <v>ML1138</v>
+        <v>DL1056</v>
       </c>
       <c r="C27" t="str">
-        <v>UOZE SWIMMER GILL</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　テナガピンク</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1800,7 +1800,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>650</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1809,13 +1809,13 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>GILL</v>
+        <v>テナガピンク</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>4550133464287</v>
       </c>
       <c r="M27" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,16 +1832,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>MLD11738</v>
+        <v>DLD10580</v>
       </c>
       <c r="B28" t="str">
-        <v>ML1138</v>
+        <v>DL1056</v>
       </c>
       <c r="C28" t="str">
-        <v>UOZE SWIMMER SMOKE SHAD</v>
+        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　パールスモーク</v>
       </c>
       <c r="D28" t="str">
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1853,7 +1853,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>650</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1862,13 +1862,13 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>SMOKE SHAD</v>
+        <v>パールスモーク</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>4550133464294</v>
       </c>
       <c r="M28" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,16 +1885,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>MLD11739</v>
+        <v>DLD10670</v>
       </c>
       <c r="B29" t="str">
-        <v>ML1138</v>
+        <v>DL1063</v>
       </c>
       <c r="C29" t="str">
-        <v>UOZE SWIMMER GOLDEN SHINER</v>
+        <v>ＢＨカバージグ６ｇ　グリーンパンプキン</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1906,7 +1906,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>550</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1915,13 +1915,13 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>GOLDEN SHINER</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>4550133505911</v>
       </c>
       <c r="M29" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,16 +1938,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>MLD11740</v>
+        <v>DLD10671</v>
       </c>
       <c r="B30" t="str">
-        <v>ML1138</v>
+        <v>DL1063</v>
       </c>
       <c r="C30" t="str">
-        <v>UOZE SWIMMER GURIPAN</v>
+        <v>ＢＨカバージグ６ｇ　グリパンピンク</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>550</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1968,13 +1968,13 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>GURIPAN</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>4550133505928</v>
       </c>
       <c r="M30" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MLD11741</v>
+        <v>DLD10672</v>
       </c>
       <c r="B31" t="str">
-        <v>ML1138</v>
+        <v>DL1063</v>
       </c>
       <c r="C31" t="str">
-        <v>UOZE SWIMMER BLACK BLUE</v>
+        <v>ＢＨカバージグ６ｇ　テナガエビ</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -2012,7 +2012,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>550</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -2021,13 +2021,13 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>BLACK BLUE</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>4550133505935</v>
       </c>
       <c r="M31" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,16 +2044,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MLD11742</v>
+        <v>DLD10673</v>
       </c>
       <c r="B32" t="str">
-        <v>ML1138</v>
+        <v>DL1063</v>
       </c>
       <c r="C32" t="str">
-        <v>UOZE SWIMMER SEXY SHAD</v>
+        <v>ＢＨカバージグ６ｇ　ゴリ</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>550</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -2074,13 +2074,13 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>SEXY SHAD</v>
+        <v>ゴリ</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>4550133505942</v>
       </c>
       <c r="M32" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,16 +2097,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MLD11743</v>
+        <v>DLD10674</v>
       </c>
       <c r="B33" t="str">
-        <v>ML1138</v>
+        <v>DL1063</v>
       </c>
       <c r="C33" t="str">
-        <v>UOZE SWIMMER REACTION CHART</v>
+        <v>ＢＨカバージグ６ｇ　沼ザリ</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -2118,7 +2118,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
+        <v>550</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -2127,13 +2127,13 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>REACTION CHART</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>4550133505959</v>
       </c>
       <c r="M33" t="str">
-        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
+        <v/>
       </c>
       <c r="N33" t="str">
         <v/>
@@ -2150,16 +2150,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>DLD10557</v>
+        <v>DLD10675</v>
       </c>
       <c r="B34" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C34" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　グ　リーンパンプキンブルーフレーク</v>
+        <v>ＢＨカバージグ６ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D34" t="str">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -2171,7 +2171,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -2180,10 +2180,10 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>リーンパンプキンブルーフレーク</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L34" t="str">
-        <v>4550133464065</v>
+        <v>4550133505966</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -2203,16 +2203,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>DLD10558</v>
+        <v>DLD10676</v>
       </c>
       <c r="B35" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C35" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　チラシ</v>
+        <v>ＢＨカバージグ６ｇ　ブラック</v>
       </c>
       <c r="D35" t="str">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -2224,7 +2224,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -2233,10 +2233,10 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>チラシ</v>
+        <v>ブラック</v>
       </c>
       <c r="L35" t="str">
-        <v>4550133464072</v>
+        <v>4550133505973</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -2256,16 +2256,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DLD10559</v>
+        <v>DLD10677</v>
       </c>
       <c r="B36" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C36" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　スジエビ</v>
+        <v>ＢＨカバージグ６ｇ　サマークロー</v>
       </c>
       <c r="D36" t="str">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -2277,7 +2277,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -2286,10 +2286,10 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>スジエビ</v>
+        <v>サマークロー</v>
       </c>
       <c r="L36" t="str">
-        <v>4550133464089</v>
+        <v>4550133505980</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -2309,16 +2309,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>DLD10560</v>
+        <v>DLD10678</v>
       </c>
       <c r="B37" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C37" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　ヌマザリ</v>
+        <v>ＢＨカバージグ６ｇ　マッディスペシャル</v>
       </c>
       <c r="D37" t="str">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -2330,7 +2330,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -2339,10 +2339,10 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>ヌマザリ</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L37" t="str">
-        <v>4550133464096</v>
+        <v>4550133505997</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -2362,16 +2362,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DLD10561</v>
+        <v>DLD10679</v>
       </c>
       <c r="B38" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C38" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　サマークロー</v>
+        <v>ＢＨカバージグ６ｇ　北産海老</v>
       </c>
       <c r="D38" t="str">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>サマークロー</v>
+        <v>北産海老</v>
       </c>
       <c r="L38" t="str">
-        <v>4550133464102</v>
+        <v>4550133506000</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -2415,16 +2415,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>DLD10562</v>
+        <v>DLD10680</v>
       </c>
       <c r="B39" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C39" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　シナモンブルーフレーク</v>
+        <v>ＢＨカバージグ６ｇ　キタサンホワイト</v>
       </c>
       <c r="D39" t="str">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -2445,10 +2445,10 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>シナモンブルーフレーク</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L39" t="str">
-        <v>4550133464119</v>
+        <v>4550133506017</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2468,16 +2468,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>DLD10563</v>
+        <v>DLD10681</v>
       </c>
       <c r="B40" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C40" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　テナガピンク</v>
+        <v>ＢＨカバージグ８ｇ　グリーンパンプキン</v>
       </c>
       <c r="D40" t="str">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -2489,7 +2489,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -2498,10 +2498,10 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>テナガピンク</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L40" t="str">
-        <v>4550133464126</v>
+        <v>4550133506024</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2521,16 +2521,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DLD10564</v>
+        <v>DLD10682</v>
       </c>
       <c r="B41" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C41" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　２．７ｇ　パールスモーク</v>
+        <v>ＢＨカバージグ８ｇ　グリパンピンク</v>
       </c>
       <c r="D41" t="str">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -2542,7 +2542,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2551,10 +2551,10 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>パールスモーク</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L41" t="str">
-        <v>4550133464133</v>
+        <v>4550133506031</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DLD10565</v>
+        <v>DLD10683</v>
       </c>
       <c r="B42" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C42" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　グ　リーンパンプキンブルーフレーク</v>
+        <v>ＢＨカバージグ８ｇ　テナガエビ</v>
       </c>
       <c r="D42" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2595,7 +2595,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -2604,10 +2604,10 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>リーンパンプキンブルーフレーク</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L42" t="str">
-        <v>4550133464140</v>
+        <v>4550133506048</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2627,16 +2627,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DLD10566</v>
+        <v>DLD10684</v>
       </c>
       <c r="B43" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C43" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　チラシ</v>
+        <v>ＢＨカバージグ８ｇ　ゴリ</v>
       </c>
       <c r="D43" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2648,7 +2648,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2657,10 +2657,10 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>チラシ</v>
+        <v>ゴリ</v>
       </c>
       <c r="L43" t="str">
-        <v>4550133464157</v>
+        <v>4550133506055</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2680,16 +2680,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>DLD10567</v>
+        <v>DLD10685</v>
       </c>
       <c r="B44" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C44" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　スジエビ</v>
+        <v>ＢＨカバージグ８ｇ　沼ザリ</v>
       </c>
       <c r="D44" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2701,7 +2701,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2710,10 +2710,10 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>スジエビ</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L44" t="str">
-        <v>4550133464164</v>
+        <v>4550133506062</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2733,16 +2733,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DLD10568</v>
+        <v>DLD10686</v>
       </c>
       <c r="B45" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C45" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　ヌマザリ</v>
+        <v>ＢＨカバージグ８ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D45" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2754,7 +2754,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2763,10 +2763,10 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>ヌマザリ</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L45" t="str">
-        <v>4550133464171</v>
+        <v>4550133506079</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2786,16 +2786,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DLD10569</v>
+        <v>DLD10687</v>
       </c>
       <c r="B46" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C46" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　サマークロー</v>
+        <v>ＢＨカバージグ８ｇ　ブラック</v>
       </c>
       <c r="D46" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2816,10 +2816,10 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>サマークロー</v>
+        <v>ブラック</v>
       </c>
       <c r="L46" t="str">
-        <v>4550133464188</v>
+        <v>4550133506086</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -2839,16 +2839,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>DLD10570</v>
+        <v>DLD10688</v>
       </c>
       <c r="B47" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C47" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　シナモンブルーフレーク</v>
+        <v>ＢＨカバージグ８ｇ　サマークロー</v>
       </c>
       <c r="D47" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2860,7 +2860,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2869,10 +2869,10 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>シナモンブルーフレーク</v>
+        <v>サマークロー</v>
       </c>
       <c r="L47" t="str">
-        <v>4550133464195</v>
+        <v>4550133506093</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2892,16 +2892,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>DLD10571</v>
+        <v>DLD10689</v>
       </c>
       <c r="B48" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C48" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　テナガピンク</v>
+        <v>ＢＨカバージグ８ｇ　マッディスペシャル</v>
       </c>
       <c r="D48" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2913,7 +2913,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2922,10 +2922,10 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>テナガピンク</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L48" t="str">
-        <v>4550133464201</v>
+        <v>4550133506109</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -2945,16 +2945,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>DLD10572</v>
+        <v>DLD10690</v>
       </c>
       <c r="B49" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C49" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　３．５ｇ　パールスモーク</v>
+        <v>ＢＨカバージグ８ｇ　北産海老</v>
       </c>
       <c r="D49" t="str">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2966,7 +2966,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2975,10 +2975,10 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>パールスモーク</v>
+        <v>北産海老</v>
       </c>
       <c r="L49" t="str">
-        <v>4550133464218</v>
+        <v>4550133506116</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -2998,16 +2998,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>DLD10573</v>
+        <v>DLD10691</v>
       </c>
       <c r="B50" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C50" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　グ　リーンパンプキンブルーフレーク</v>
+        <v>ＢＨカバージグ８ｇ　キタサンホワイト</v>
       </c>
       <c r="D50" t="str">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -3019,7 +3019,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -3028,10 +3028,10 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>リーンパンプキンブルーフレーク</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L50" t="str">
-        <v>4550133464225</v>
+        <v>4550133506123</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -3051,16 +3051,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>DLD10574</v>
+        <v>DLD10692</v>
       </c>
       <c r="B51" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C51" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　チラシ</v>
+        <v>ＢＨカバージグ１０ｇ　グリーンパンプキン</v>
       </c>
       <c r="D51" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -3081,10 +3081,10 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>チラシ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L51" t="str">
-        <v>4550133464232</v>
+        <v>4550133506130</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -3104,16 +3104,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>DLD10575</v>
+        <v>DLD10693</v>
       </c>
       <c r="B52" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C52" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　スジエビ</v>
+        <v>ＢＨカバージグ１０ｇ　グリパンピンク</v>
       </c>
       <c r="D52" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -3125,7 +3125,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -3134,10 +3134,10 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>スジエビ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L52" t="str">
-        <v>4550133464249</v>
+        <v>4550133506147</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -3157,16 +3157,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>DLD10576</v>
+        <v>DLD10694</v>
       </c>
       <c r="B53" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C53" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　ヌマザリ</v>
+        <v>ＢＨカバージグ１０ｇ　テナガエビ</v>
       </c>
       <c r="D53" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -3187,10 +3187,10 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>ヌマザリ</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L53" t="str">
-        <v>4550133464256</v>
+        <v>4550133506154</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -3210,16 +3210,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>DLD10577</v>
+        <v>DLD10695</v>
       </c>
       <c r="B54" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C54" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　サマークロー</v>
+        <v>ＢＨカバージグ１０ｇ　ゴリ</v>
       </c>
       <c r="D54" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -3240,10 +3240,10 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>サマークロー</v>
+        <v>ゴリ</v>
       </c>
       <c r="L54" t="str">
-        <v>4550133464263</v>
+        <v>4550133506161</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -3263,16 +3263,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>DLD10578</v>
+        <v>DLD10696</v>
       </c>
       <c r="B55" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C55" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　シナモンブルーフレーク</v>
+        <v>ＢＨカバージグ１０ｇ　沼ザリ</v>
       </c>
       <c r="D55" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -3284,7 +3284,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -3293,10 +3293,10 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>シナモンブルーフレーク</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L55" t="str">
-        <v>4550133464270</v>
+        <v>4550133506178</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -3316,16 +3316,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>DLD10579</v>
+        <v>DLD10697</v>
       </c>
       <c r="B56" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C56" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　テナガピンク</v>
+        <v>ＢＨカバージグ１０ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D56" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -3346,10 +3346,10 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>テナガピンク</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L56" t="str">
-        <v>4550133464287</v>
+        <v>4550133506185</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -3369,16 +3369,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>DLD10580</v>
+        <v>DLD10698</v>
       </c>
       <c r="B57" t="str">
-        <v>DL1056</v>
+        <v>DL1063</v>
       </c>
       <c r="C57" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグ　４．７ｇ　パールスモーク</v>
+        <v>ＢＨカバージグ１０ｇ　ブラック</v>
       </c>
       <c r="D57" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -3390,7 +3390,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -3399,10 +3399,10 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>パールスモーク</v>
+        <v>ブラック</v>
       </c>
       <c r="L57" t="str">
-        <v>4550133464294</v>
+        <v>4550133506192</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -3422,16 +3422,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>DLD10670</v>
+        <v>DLD10699</v>
       </c>
       <c r="B58" t="str">
         <v>DL1063</v>
       </c>
       <c r="C58" t="str">
-        <v>ＢＨカバージグ６ｇ　グリーンパンプキン</v>
+        <v>ＢＨカバージグ１０ｇ　サマークロー</v>
       </c>
       <c r="D58" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -3452,10 +3452,10 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L58" t="str">
-        <v>4550133505911</v>
+        <v>4550133506208</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -3475,16 +3475,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>DLD10671</v>
+        <v>DLD10700</v>
       </c>
       <c r="B59" t="str">
         <v>DL1063</v>
       </c>
       <c r="C59" t="str">
-        <v>ＢＨカバージグ６ｇ　グリパンピンク</v>
+        <v>ＢＨカバージグ１０ｇ　マッディスペシャル</v>
       </c>
       <c r="D59" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -3505,10 +3505,10 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>グリパンピンク</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L59" t="str">
-        <v>4550133505928</v>
+        <v>4550133506215</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -3528,16 +3528,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>DLD10672</v>
+        <v>DLD10701</v>
       </c>
       <c r="B60" t="str">
         <v>DL1063</v>
       </c>
       <c r="C60" t="str">
-        <v>ＢＨカバージグ６ｇ　テナガエビ</v>
+        <v>ＢＨカバージグ１０ｇ　北産海老</v>
       </c>
       <c r="D60" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -3558,10 +3558,10 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>テナガエビ</v>
+        <v>北産海老</v>
       </c>
       <c r="L60" t="str">
-        <v>4550133505935</v>
+        <v>4550133506222</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -3581,16 +3581,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>DLD10673</v>
+        <v>DLD10702</v>
       </c>
       <c r="B61" t="str">
         <v>DL1063</v>
       </c>
       <c r="C61" t="str">
-        <v>ＢＨカバージグ６ｇ　ゴリ</v>
+        <v>ＢＨカバージグ１０ｇ　キタサンホワイト</v>
       </c>
       <c r="D61" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -3611,10 +3611,10 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>ゴリ</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L61" t="str">
-        <v>4550133505942</v>
+        <v>4550133506239</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>DLD10674</v>
+        <v>DLD10703</v>
       </c>
       <c r="B62" t="str">
         <v>DL1063</v>
       </c>
       <c r="C62" t="str">
-        <v>ＢＨカバージグ６ｇ　沼ザリ</v>
+        <v>ＢＨカバージグ１４ｇ　グリーンパンプキン</v>
       </c>
       <c r="D62" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -3664,10 +3664,10 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>沼ザリ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L62" t="str">
-        <v>4550133505959</v>
+        <v>4550133506246</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -3687,16 +3687,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>DLD10675</v>
+        <v>DLD10704</v>
       </c>
       <c r="B63" t="str">
         <v>DL1063</v>
       </c>
       <c r="C63" t="str">
-        <v>ＢＨカバージグ６ｇ　スポーンシュリンプ</v>
+        <v>ＢＨカバージグ１４ｇ　グリパンピンク</v>
       </c>
       <c r="D63" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -3717,10 +3717,10 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L63" t="str">
-        <v>4550133505966</v>
+        <v>4550133506253</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -3740,16 +3740,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>DLD10676</v>
+        <v>DLD10705</v>
       </c>
       <c r="B64" t="str">
         <v>DL1063</v>
       </c>
       <c r="C64" t="str">
-        <v>ＢＨカバージグ６ｇ　ブラック</v>
+        <v>ＢＨカバージグ１４ｇ　テナガエビ</v>
       </c>
       <c r="D64" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -3770,10 +3770,10 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>ブラック</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L64" t="str">
-        <v>4550133505973</v>
+        <v>4550133506260</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -3793,16 +3793,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>DLD10677</v>
+        <v>DLD10706</v>
       </c>
       <c r="B65" t="str">
         <v>DL1063</v>
       </c>
       <c r="C65" t="str">
-        <v>ＢＨカバージグ６ｇ　サマークロー</v>
+        <v>ＢＨカバージグ１４ｇ　ゴリ</v>
       </c>
       <c r="D65" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -3823,10 +3823,10 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>サマークロー</v>
+        <v>ゴリ</v>
       </c>
       <c r="L65" t="str">
-        <v>4550133505980</v>
+        <v>4550133506277</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -3846,16 +3846,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>DLD10678</v>
+        <v>DLD10707</v>
       </c>
       <c r="B66" t="str">
         <v>DL1063</v>
       </c>
       <c r="C66" t="str">
-        <v>ＢＨカバージグ６ｇ　マッディスペシャル</v>
+        <v>ＢＨカバージグ１４ｇ　沼ザリ</v>
       </c>
       <c r="D66" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -3876,10 +3876,10 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>マッディスペシャル</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L66" t="str">
-        <v>4550133505997</v>
+        <v>4550133506284</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3899,16 +3899,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>DLD10679</v>
+        <v>DLD10708</v>
       </c>
       <c r="B67" t="str">
         <v>DL1063</v>
       </c>
       <c r="C67" t="str">
-        <v>ＢＨカバージグ６ｇ　北産海老</v>
+        <v>ＢＨカバージグ１４ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D67" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -3929,10 +3929,10 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>北産海老</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L67" t="str">
-        <v>4550133506000</v>
+        <v>4550133506291</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3952,16 +3952,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>DLD10680</v>
+        <v>DLD10709</v>
       </c>
       <c r="B68" t="str">
         <v>DL1063</v>
       </c>
       <c r="C68" t="str">
-        <v>ＢＨカバージグ６ｇ　キタサンホワイト</v>
+        <v>ＢＨカバージグ１４ｇ　ブラック</v>
       </c>
       <c r="D68" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -3982,10 +3982,10 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>キタサンホワイト</v>
+        <v>ブラック</v>
       </c>
       <c r="L68" t="str">
-        <v>4550133506017</v>
+        <v>4550133506307</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -4005,16 +4005,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>DLD10681</v>
+        <v>DLD10710</v>
       </c>
       <c r="B69" t="str">
         <v>DL1063</v>
       </c>
       <c r="C69" t="str">
-        <v>ＢＨカバージグ８ｇ　グリーンパンプキン</v>
+        <v>ＢＨカバージグ１４ｇ　サマークロー</v>
       </c>
       <c r="D69" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -4035,10 +4035,10 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L69" t="str">
-        <v>4550133506024</v>
+        <v>4550133506314</v>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -4058,16 +4058,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>DLD10682</v>
+        <v>DLD10711</v>
       </c>
       <c r="B70" t="str">
         <v>DL1063</v>
       </c>
       <c r="C70" t="str">
-        <v>ＢＨカバージグ８ｇ　グリパンピンク</v>
+        <v>ＢＨカバージグ１４ｇ　マッディスペシャル</v>
       </c>
       <c r="D70" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -4088,10 +4088,10 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>グリパンピンク</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L70" t="str">
-        <v>4550133506031</v>
+        <v>4550133506321</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -4111,16 +4111,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>DLD10683</v>
+        <v>DLD10712</v>
       </c>
       <c r="B71" t="str">
         <v>DL1063</v>
       </c>
       <c r="C71" t="str">
-        <v>ＢＨカバージグ８ｇ　テナガエビ</v>
+        <v>ＢＨカバージグ１４ｇ　北産海老</v>
       </c>
       <c r="D71" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -4141,10 +4141,10 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>テナガエビ</v>
+        <v>北産海老</v>
       </c>
       <c r="L71" t="str">
-        <v>4550133506048</v>
+        <v>4550133506338</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -4164,16 +4164,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>DLD10684</v>
+        <v>DLD10713</v>
       </c>
       <c r="B72" t="str">
         <v>DL1063</v>
       </c>
       <c r="C72" t="str">
-        <v>ＢＨカバージグ８ｇ　ゴリ</v>
+        <v>ＢＨカバージグ１４ｇ　キタサンホワイト</v>
       </c>
       <c r="D72" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -4194,10 +4194,10 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>ゴリ</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L72" t="str">
-        <v>4550133506055</v>
+        <v>4550133506345</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -4217,16 +4217,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>DLD10685</v>
+        <v>DLD10714</v>
       </c>
       <c r="B73" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C73" t="str">
-        <v>ＢＨカバージグ８ｇ　沼ザリ</v>
+        <v>ＢＨマルチジグ６ｇ　グリーンパンプキン</v>
       </c>
       <c r="D73" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -4247,10 +4247,10 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>沼ザリ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L73" t="str">
-        <v>4550133506062</v>
+        <v>4550133504808</v>
       </c>
       <c r="M73" t="str">
         <v/>
@@ -4270,16 +4270,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>DLD10686</v>
+        <v>DLD10715</v>
       </c>
       <c r="B74" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C74" t="str">
-        <v>ＢＨカバージグ８ｇ　スポーンシュリンプ</v>
+        <v>ＢＨマルチジグ６ｇ　グリパンピンク</v>
       </c>
       <c r="D74" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -4300,10 +4300,10 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L74" t="str">
-        <v>4550133506079</v>
+        <v>4550133504815</v>
       </c>
       <c r="M74" t="str">
         <v/>
@@ -4323,16 +4323,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>DLD10687</v>
+        <v>DLD10716</v>
       </c>
       <c r="B75" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C75" t="str">
-        <v>ＢＨカバージグ８ｇ　ブラック</v>
+        <v>ＢＨマルチジグ６ｇ　テナガエビ</v>
       </c>
       <c r="D75" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -4353,10 +4353,10 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>ブラック</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L75" t="str">
-        <v>4550133506086</v>
+        <v>4550133504822</v>
       </c>
       <c r="M75" t="str">
         <v/>
@@ -4376,16 +4376,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DLD10688</v>
+        <v>DLD10717</v>
       </c>
       <c r="B76" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C76" t="str">
-        <v>ＢＨカバージグ８ｇ　サマークロー</v>
+        <v>ＢＨマルチジグ６ｇ　ゴリ</v>
       </c>
       <c r="D76" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -4406,10 +4406,10 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>サマークロー</v>
+        <v>ゴリ</v>
       </c>
       <c r="L76" t="str">
-        <v>4550133506093</v>
+        <v>4550133504839</v>
       </c>
       <c r="M76" t="str">
         <v/>
@@ -4429,16 +4429,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DLD10689</v>
+        <v>DLD10718</v>
       </c>
       <c r="B77" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C77" t="str">
-        <v>ＢＨカバージグ８ｇ　マッディスペシャル</v>
+        <v>ＢＨマルチジグ６ｇ　沼ザリ</v>
       </c>
       <c r="D77" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -4459,10 +4459,10 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>マッディスペシャル</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L77" t="str">
-        <v>4550133506109</v>
+        <v>4550133504846</v>
       </c>
       <c r="M77" t="str">
         <v/>
@@ -4482,16 +4482,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>DLD10690</v>
+        <v>DLD10719</v>
       </c>
       <c r="B78" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C78" t="str">
-        <v>ＢＨカバージグ８ｇ　北産海老</v>
+        <v>ＢＨマルチジグ６ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D78" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -4512,10 +4512,10 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>北産海老</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L78" t="str">
-        <v>4550133506116</v>
+        <v>4550133504853</v>
       </c>
       <c r="M78" t="str">
         <v/>
@@ -4535,16 +4535,16 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>DLD10691</v>
+        <v>DLD10720</v>
       </c>
       <c r="B79" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C79" t="str">
-        <v>ＢＨカバージグ８ｇ　キタサンホワイト</v>
+        <v>ＢＨマルチジグ６ｇ　ブラック</v>
       </c>
       <c r="D79" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -4565,10 +4565,10 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>キタサンホワイト</v>
+        <v>ブラック</v>
       </c>
       <c r="L79" t="str">
-        <v>4550133506123</v>
+        <v>4550133504860</v>
       </c>
       <c r="M79" t="str">
         <v/>
@@ -4588,16 +4588,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DLD10692</v>
+        <v>DLD10721</v>
       </c>
       <c r="B80" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C80" t="str">
-        <v>ＢＨカバージグ１０ｇ　グリーンパンプキン</v>
+        <v>ＢＨマルチジグ６ｇ　サマークロー</v>
       </c>
       <c r="D80" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -4618,10 +4618,10 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L80" t="str">
-        <v>4550133506130</v>
+        <v>4550133504877</v>
       </c>
       <c r="M80" t="str">
         <v/>
@@ -4641,16 +4641,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>DLD10693</v>
+        <v>DLD10722</v>
       </c>
       <c r="B81" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C81" t="str">
-        <v>ＢＨカバージグ１０ｇ　グリパンピンク</v>
+        <v>ＢＨマルチジグ６ｇ　マッディスペシャル</v>
       </c>
       <c r="D81" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -4671,10 +4671,10 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>グリパンピンク</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L81" t="str">
-        <v>4550133506147</v>
+        <v>4550133504884</v>
       </c>
       <c r="M81" t="str">
         <v/>
@@ -4694,16 +4694,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>DLD10694</v>
+        <v>DLD10723</v>
       </c>
       <c r="B82" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C82" t="str">
-        <v>ＢＨカバージグ１０ｇ　テナガエビ</v>
+        <v>ＢＨマルチジグ６ｇ　北産海老</v>
       </c>
       <c r="D82" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -4724,10 +4724,10 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>テナガエビ</v>
+        <v>北産海老</v>
       </c>
       <c r="L82" t="str">
-        <v>4550133506154</v>
+        <v>4550133504891</v>
       </c>
       <c r="M82" t="str">
         <v/>
@@ -4747,16 +4747,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>DLD10695</v>
+        <v>DLD10724</v>
       </c>
       <c r="B83" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C83" t="str">
-        <v>ＢＨカバージグ１０ｇ　ゴリ</v>
+        <v>ＢＨマルチジグ６ｇ　キタサンホワイト</v>
       </c>
       <c r="D83" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -4777,10 +4777,10 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>ゴリ</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L83" t="str">
-        <v>4550133506161</v>
+        <v>4550133504907</v>
       </c>
       <c r="M83" t="str">
         <v/>
@@ -4800,16 +4800,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>DLD10696</v>
+        <v>DLD10725</v>
       </c>
       <c r="B84" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C84" t="str">
-        <v>ＢＨカバージグ１０ｇ　沼ザリ</v>
+        <v>ＢＨマルチジグ８ｇ　グリーンパンプキン</v>
       </c>
       <c r="D84" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -4830,10 +4830,10 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>沼ザリ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L84" t="str">
-        <v>4550133506178</v>
+        <v>4550133504914</v>
       </c>
       <c r="M84" t="str">
         <v/>
@@ -4853,16 +4853,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>DLD10697</v>
+        <v>DLD10726</v>
       </c>
       <c r="B85" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C85" t="str">
-        <v>ＢＨカバージグ１０ｇ　スポーンシュリンプ</v>
+        <v>ＢＨマルチジグ８ｇ　グリパンピンク</v>
       </c>
       <c r="D85" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -4883,10 +4883,10 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L85" t="str">
-        <v>4550133506185</v>
+        <v>4550133504921</v>
       </c>
       <c r="M85" t="str">
         <v/>
@@ -4906,16 +4906,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>DLD10698</v>
+        <v>DLD10727</v>
       </c>
       <c r="B86" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C86" t="str">
-        <v>ＢＨカバージグ１０ｇ　ブラック</v>
+        <v>ＢＨマルチジグ８ｇ　テナガエビ</v>
       </c>
       <c r="D86" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -4936,10 +4936,10 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>ブラック</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L86" t="str">
-        <v>4550133506192</v>
+        <v>4550133504938</v>
       </c>
       <c r="M86" t="str">
         <v/>
@@ -4959,16 +4959,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>DLD10699</v>
+        <v>DLD10728</v>
       </c>
       <c r="B87" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C87" t="str">
-        <v>ＢＨカバージグ１０ｇ　サマークロー</v>
+        <v>ＢＨマルチジグ８ｇ　ゴリ</v>
       </c>
       <c r="D87" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -4989,10 +4989,10 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>サマークロー</v>
+        <v>ゴリ</v>
       </c>
       <c r="L87" t="str">
-        <v>4550133506208</v>
+        <v>4550133504945</v>
       </c>
       <c r="M87" t="str">
         <v/>
@@ -5012,16 +5012,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DLD10700</v>
+        <v>DLD10729</v>
       </c>
       <c r="B88" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C88" t="str">
-        <v>ＢＨカバージグ１０ｇ　マッディスペシャル</v>
+        <v>ＢＨマルチジグ８ｇ　沼ザリ</v>
       </c>
       <c r="D88" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -5042,10 +5042,10 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>マッディスペシャル</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L88" t="str">
-        <v>4550133506215</v>
+        <v>4550133504952</v>
       </c>
       <c r="M88" t="str">
         <v/>
@@ -5065,16 +5065,16 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>DLD10701</v>
+        <v>DLD10730</v>
       </c>
       <c r="B89" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C89" t="str">
-        <v>ＢＨカバージグ１０ｇ　北産海老</v>
+        <v>ＢＨマルチジグ８ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D89" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -5095,10 +5095,10 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>北産海老</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L89" t="str">
-        <v>4550133506222</v>
+        <v>4550133504969</v>
       </c>
       <c r="M89" t="str">
         <v/>
@@ -5118,16 +5118,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>DLD10702</v>
+        <v>DLD10731</v>
       </c>
       <c r="B90" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C90" t="str">
-        <v>ＢＨカバージグ１０ｇ　キタサンホワイト</v>
+        <v>ＢＨマルチジグ８ｇ　ブラック</v>
       </c>
       <c r="D90" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -5148,10 +5148,10 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>キタサンホワイト</v>
+        <v>ブラック</v>
       </c>
       <c r="L90" t="str">
-        <v>4550133506239</v>
+        <v>4550133504976</v>
       </c>
       <c r="M90" t="str">
         <v/>
@@ -5171,16 +5171,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>DLD10703</v>
+        <v>DLD10732</v>
       </c>
       <c r="B91" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C91" t="str">
-        <v>ＢＨカバージグ１４ｇ　グリーンパンプキン</v>
+        <v>ＢＨマルチジグ８ｇ　サマークロー</v>
       </c>
       <c r="D91" t="str">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -5201,10 +5201,10 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L91" t="str">
-        <v>4550133506246</v>
+        <v>4550133504983</v>
       </c>
       <c r="M91" t="str">
         <v/>
@@ -5224,16 +5224,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>DLD10704</v>
+        <v>DLD10733</v>
       </c>
       <c r="B92" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C92" t="str">
-        <v>ＢＨカバージグ１４ｇ　グリパンピンク</v>
+        <v>ＢＨマルチジグ８ｇ　マッディスペシャル</v>
       </c>
       <c r="D92" t="str">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -5254,10 +5254,10 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>グリパンピンク</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L92" t="str">
-        <v>4550133506253</v>
+        <v>4550133504990</v>
       </c>
       <c r="M92" t="str">
         <v/>
@@ -5277,16 +5277,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>DLD10705</v>
+        <v>DLD10734</v>
       </c>
       <c r="B93" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C93" t="str">
-        <v>ＢＨカバージグ１４ｇ　テナガエビ</v>
+        <v>ＢＨマルチジグ８ｇ　北産海老</v>
       </c>
       <c r="D93" t="str">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -5307,10 +5307,10 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>テナガエビ</v>
+        <v>北産海老</v>
       </c>
       <c r="L93" t="str">
-        <v>4550133506260</v>
+        <v>4550133505003</v>
       </c>
       <c r="M93" t="str">
         <v/>
@@ -5330,16 +5330,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>DLD10706</v>
+        <v>DLD10735</v>
       </c>
       <c r="B94" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C94" t="str">
-        <v>ＢＨカバージグ１４ｇ　ゴリ</v>
+        <v>ＢＨマルチジグ８ｇ　キタサンホワイト</v>
       </c>
       <c r="D94" t="str">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -5360,10 +5360,10 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>ゴリ</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L94" t="str">
-        <v>4550133506277</v>
+        <v>4550133505010</v>
       </c>
       <c r="M94" t="str">
         <v/>
@@ -5383,16 +5383,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DLD10707</v>
+        <v>DLD10736</v>
       </c>
       <c r="B95" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C95" t="str">
-        <v>ＢＨカバージグ１４ｇ　沼ザリ</v>
+        <v>ＢＨマルチジグ１０ｇ　グリーンパンプキン</v>
       </c>
       <c r="D95" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -5413,10 +5413,10 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>沼ザリ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L95" t="str">
-        <v>4550133506284</v>
+        <v>4550133505027</v>
       </c>
       <c r="M95" t="str">
         <v/>
@@ -5436,16 +5436,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>DLD10708</v>
+        <v>DLD10737</v>
       </c>
       <c r="B96" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C96" t="str">
-        <v>ＢＨカバージグ１４ｇ　スポーンシュリンプ</v>
+        <v>ＢＨマルチジグ１０ｇ　グリパンピンク</v>
       </c>
       <c r="D96" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -5466,10 +5466,10 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L96" t="str">
-        <v>4550133506291</v>
+        <v>4550133505034</v>
       </c>
       <c r="M96" t="str">
         <v/>
@@ -5489,16 +5489,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>DLD10709</v>
+        <v>DLD10738</v>
       </c>
       <c r="B97" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C97" t="str">
-        <v>ＢＨカバージグ１４ｇ　ブラック</v>
+        <v>ＢＨマルチジグ１０ｇ　テナガエビ</v>
       </c>
       <c r="D97" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -5519,10 +5519,10 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>ブラック</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L97" t="str">
-        <v>4550133506307</v>
+        <v>4550133505041</v>
       </c>
       <c r="M97" t="str">
         <v/>
@@ -5542,16 +5542,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>DLD10710</v>
+        <v>DLD10739</v>
       </c>
       <c r="B98" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C98" t="str">
-        <v>ＢＨカバージグ１４ｇ　サマークロー</v>
+        <v>ＢＨマルチジグ１０ｇ　ゴリ</v>
       </c>
       <c r="D98" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -5572,10 +5572,10 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>サマークロー</v>
+        <v>ゴリ</v>
       </c>
       <c r="L98" t="str">
-        <v>4550133506314</v>
+        <v>4550133505058</v>
       </c>
       <c r="M98" t="str">
         <v/>
@@ -5595,16 +5595,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>DLD10711</v>
+        <v>DLD10740</v>
       </c>
       <c r="B99" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C99" t="str">
-        <v>ＢＨカバージグ１４ｇ　マッディスペシャル</v>
+        <v>ＢＨマルチジグ１０ｇ　沼ザリ</v>
       </c>
       <c r="D99" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -5625,10 +5625,10 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>マッディスペシャル</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L99" t="str">
-        <v>4550133506321</v>
+        <v>4550133505065</v>
       </c>
       <c r="M99" t="str">
         <v/>
@@ -5648,16 +5648,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>DLD10712</v>
+        <v>DLD10741</v>
       </c>
       <c r="B100" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C100" t="str">
-        <v>ＢＨカバージグ１４ｇ　北産海老</v>
+        <v>ＢＨマルチジグ１０ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D100" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -5678,10 +5678,10 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>北産海老</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L100" t="str">
-        <v>4550133506338</v>
+        <v>4550133505072</v>
       </c>
       <c r="M100" t="str">
         <v/>
@@ -5701,16 +5701,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>DLD10713</v>
+        <v>DLD10742</v>
       </c>
       <c r="B101" t="str">
-        <v>DL1063</v>
+        <v>DL1064</v>
       </c>
       <c r="C101" t="str">
-        <v>ＢＨカバージグ１４ｇ　キタサンホワイト</v>
+        <v>ＢＨマルチジグ１０ｇ　ブラック</v>
       </c>
       <c r="D101" t="str">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -5731,10 +5731,10 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>キタサンホワイト</v>
+        <v>ブラック</v>
       </c>
       <c r="L101" t="str">
-        <v>4550133506345</v>
+        <v>4550133505089</v>
       </c>
       <c r="M101" t="str">
         <v/>
@@ -5754,16 +5754,16 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>DLD10714</v>
+        <v>DLD10743</v>
       </c>
       <c r="B102" t="str">
         <v>DL1064</v>
       </c>
       <c r="C102" t="str">
-        <v>ＢＨマルチジグ６ｇ　グリーンパンプキン</v>
+        <v>ＢＨマルチジグ１０ｇ　サマークロー</v>
       </c>
       <c r="D102" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -5784,10 +5784,10 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L102" t="str">
-        <v>4550133504808</v>
+        <v>4550133505096</v>
       </c>
       <c r="M102" t="str">
         <v/>
@@ -5807,16 +5807,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>DLD10715</v>
+        <v>DLD10744</v>
       </c>
       <c r="B103" t="str">
         <v>DL1064</v>
       </c>
       <c r="C103" t="str">
-        <v>ＢＨマルチジグ６ｇ　グリパンピンク</v>
+        <v>ＢＨマルチジグ１０ｇ　マッディスペシャル</v>
       </c>
       <c r="D103" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -5837,10 +5837,10 @@
         <v/>
       </c>
       <c r="K103" t="str">
-        <v>グリパンピンク</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L103" t="str">
-        <v>4550133504815</v>
+        <v>4550133505102</v>
       </c>
       <c r="M103" t="str">
         <v/>
@@ -5860,16 +5860,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>DLD10716</v>
+        <v>DLD10745</v>
       </c>
       <c r="B104" t="str">
         <v>DL1064</v>
       </c>
       <c r="C104" t="str">
-        <v>ＢＨマルチジグ６ｇ　テナガエビ</v>
+        <v>ＢＨマルチジグ１０ｇ　北産海老</v>
       </c>
       <c r="D104" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -5890,10 +5890,10 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v>テナガエビ</v>
+        <v>北産海老</v>
       </c>
       <c r="L104" t="str">
-        <v>4550133504822</v>
+        <v>4550133505119</v>
       </c>
       <c r="M104" t="str">
         <v/>
@@ -5913,16 +5913,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>DLD10717</v>
+        <v>DLD10746</v>
       </c>
       <c r="B105" t="str">
         <v>DL1064</v>
       </c>
       <c r="C105" t="str">
-        <v>ＢＨマルチジグ６ｇ　ゴリ</v>
+        <v>ＢＨマルチジグ１０ｇ　キタサンホワイト</v>
       </c>
       <c r="D105" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -5943,10 +5943,10 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <v>ゴリ</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L105" t="str">
-        <v>4550133504839</v>
+        <v>4550133505126</v>
       </c>
       <c r="M105" t="str">
         <v/>
@@ -5966,16 +5966,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>DLD10718</v>
+        <v>DLD10747</v>
       </c>
       <c r="B106" t="str">
         <v>DL1064</v>
       </c>
       <c r="C106" t="str">
-        <v>ＢＨマルチジグ６ｇ　沼ザリ</v>
+        <v>ＢＨマルチジグ１４ｇ　グリーンパンプキン</v>
       </c>
       <c r="D106" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -5996,10 +5996,10 @@
         <v/>
       </c>
       <c r="K106" t="str">
-        <v>沼ザリ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L106" t="str">
-        <v>4550133504846</v>
+        <v>4550133505133</v>
       </c>
       <c r="M106" t="str">
         <v/>
@@ -6019,16 +6019,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>DLD10719</v>
+        <v>DLD10748</v>
       </c>
       <c r="B107" t="str">
         <v>DL1064</v>
       </c>
       <c r="C107" t="str">
-        <v>ＢＨマルチジグ６ｇ　スポーンシュリンプ</v>
+        <v>ＢＨマルチジグ１４ｇ　グリパンピンク</v>
       </c>
       <c r="D107" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -6049,10 +6049,10 @@
         <v/>
       </c>
       <c r="K107" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L107" t="str">
-        <v>4550133504853</v>
+        <v>4550133505140</v>
       </c>
       <c r="M107" t="str">
         <v/>
@@ -6072,16 +6072,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>DLD10720</v>
+        <v>DLD10749</v>
       </c>
       <c r="B108" t="str">
         <v>DL1064</v>
       </c>
       <c r="C108" t="str">
-        <v>ＢＨマルチジグ６ｇ　ブラック</v>
+        <v>ＢＨマルチジグ１４ｇ　テナガエビ</v>
       </c>
       <c r="D108" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -6102,10 +6102,10 @@
         <v/>
       </c>
       <c r="K108" t="str">
-        <v>ブラック</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L108" t="str">
-        <v>4550133504860</v>
+        <v>4550133505157</v>
       </c>
       <c r="M108" t="str">
         <v/>
@@ -6125,16 +6125,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>DLD10721</v>
+        <v>DLD10750</v>
       </c>
       <c r="B109" t="str">
         <v>DL1064</v>
       </c>
       <c r="C109" t="str">
-        <v>ＢＨマルチジグ６ｇ　サマークロー</v>
+        <v>ＢＨマルチジグ１４ｇ　ゴリ</v>
       </c>
       <c r="D109" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -6155,10 +6155,10 @@
         <v/>
       </c>
       <c r="K109" t="str">
-        <v>サマークロー</v>
+        <v>ゴリ</v>
       </c>
       <c r="L109" t="str">
-        <v>4550133504877</v>
+        <v>4550133505164</v>
       </c>
       <c r="M109" t="str">
         <v/>
@@ -6178,16 +6178,16 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>DLD10722</v>
+        <v>DLD10751</v>
       </c>
       <c r="B110" t="str">
         <v>DL1064</v>
       </c>
       <c r="C110" t="str">
-        <v>ＢＨマルチジグ６ｇ　マッディスペシャル</v>
+        <v>ＢＨマルチジグ１４ｇ　沼ザリ</v>
       </c>
       <c r="D110" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -6208,10 +6208,10 @@
         <v/>
       </c>
       <c r="K110" t="str">
-        <v>マッディスペシャル</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L110" t="str">
-        <v>4550133504884</v>
+        <v>4550133505171</v>
       </c>
       <c r="M110" t="str">
         <v/>
@@ -6231,16 +6231,16 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>DLD10723</v>
+        <v>DLD10752</v>
       </c>
       <c r="B111" t="str">
         <v>DL1064</v>
       </c>
       <c r="C111" t="str">
-        <v>ＢＨマルチジグ６ｇ　北産海老</v>
+        <v>ＢＨマルチジグ１４ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D111" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -6261,10 +6261,10 @@
         <v/>
       </c>
       <c r="K111" t="str">
-        <v>北産海老</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L111" t="str">
-        <v>4550133504891</v>
+        <v>4550133505188</v>
       </c>
       <c r="M111" t="str">
         <v/>
@@ -6284,16 +6284,16 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>DLD10724</v>
+        <v>DLD10753</v>
       </c>
       <c r="B112" t="str">
         <v>DL1064</v>
       </c>
       <c r="C112" t="str">
-        <v>ＢＨマルチジグ６ｇ　キタサンホワイト</v>
+        <v>ＢＨマルチジグ１４ｇ　ブラック</v>
       </c>
       <c r="D112" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -6314,10 +6314,10 @@
         <v/>
       </c>
       <c r="K112" t="str">
-        <v>キタサンホワイト</v>
+        <v>ブラック</v>
       </c>
       <c r="L112" t="str">
-        <v>4550133504907</v>
+        <v>4550133505195</v>
       </c>
       <c r="M112" t="str">
         <v/>
@@ -6337,16 +6337,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>DLD10725</v>
+        <v>DLD10754</v>
       </c>
       <c r="B113" t="str">
         <v>DL1064</v>
       </c>
       <c r="C113" t="str">
-        <v>ＢＨマルチジグ８ｇ　グリーンパンプキン</v>
+        <v>ＢＨマルチジグ１４ｇ　サマークロー</v>
       </c>
       <c r="D113" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -6367,10 +6367,10 @@
         <v/>
       </c>
       <c r="K113" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L113" t="str">
-        <v>4550133504914</v>
+        <v>4550133505201</v>
       </c>
       <c r="M113" t="str">
         <v/>
@@ -6390,16 +6390,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>DLD10726</v>
+        <v>DLD10755</v>
       </c>
       <c r="B114" t="str">
         <v>DL1064</v>
       </c>
       <c r="C114" t="str">
-        <v>ＢＨマルチジグ８ｇ　グリパンピンク</v>
+        <v>ＢＨマルチジグ１４ｇ　マッディスペシャル</v>
       </c>
       <c r="D114" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -6420,10 +6420,10 @@
         <v/>
       </c>
       <c r="K114" t="str">
-        <v>グリパンピンク</v>
+        <v>マッディスペシャル</v>
       </c>
       <c r="L114" t="str">
-        <v>4550133504921</v>
+        <v>4550133505218</v>
       </c>
       <c r="M114" t="str">
         <v/>
@@ -6443,16 +6443,16 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>DLD10727</v>
+        <v>DLD10756</v>
       </c>
       <c r="B115" t="str">
         <v>DL1064</v>
       </c>
       <c r="C115" t="str">
-        <v>ＢＨマルチジグ８ｇ　テナガエビ</v>
+        <v>ＢＨマルチジグ１４ｇ　北産海老</v>
       </c>
       <c r="D115" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -6473,10 +6473,10 @@
         <v/>
       </c>
       <c r="K115" t="str">
-        <v>テナガエビ</v>
+        <v>北産海老</v>
       </c>
       <c r="L115" t="str">
-        <v>4550133504938</v>
+        <v>4550133505225</v>
       </c>
       <c r="M115" t="str">
         <v/>
@@ -6496,16 +6496,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>DLD10728</v>
+        <v>DLD10757</v>
       </c>
       <c r="B116" t="str">
         <v>DL1064</v>
       </c>
       <c r="C116" t="str">
-        <v>ＢＨマルチジグ８ｇ　ゴリ</v>
+        <v>ＢＨマルチジグ１４ｇ　キタサンホワイト</v>
       </c>
       <c r="D116" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -6526,10 +6526,10 @@
         <v/>
       </c>
       <c r="K116" t="str">
-        <v>ゴリ</v>
+        <v>キタサンホワイト</v>
       </c>
       <c r="L116" t="str">
-        <v>4550133504945</v>
+        <v>4550133505232</v>
       </c>
       <c r="M116" t="str">
         <v/>
@@ -6549,16 +6549,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>DLD10729</v>
+        <v>DLD10758</v>
       </c>
       <c r="B117" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C117" t="str">
-        <v>ＢＨマルチジグ８ｇ　沼ザリ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　グリーンパンプキンブルーＦＬ</v>
       </c>
       <c r="D117" t="str">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -6570,7 +6570,7 @@
         <v/>
       </c>
       <c r="H117" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -6579,10 +6579,10 @@
         <v/>
       </c>
       <c r="K117" t="str">
-        <v>沼ザリ</v>
+        <v>グリーンパンプキンブルーＦＬ</v>
       </c>
       <c r="L117" t="str">
-        <v>4550133504952</v>
+        <v>4550133464300</v>
       </c>
       <c r="M117" t="str">
         <v/>
@@ -6602,16 +6602,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>DLD10730</v>
+        <v>DLD10759</v>
       </c>
       <c r="B118" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C118" t="str">
-        <v>ＢＨマルチジグ８ｇ　スポーンシュリンプ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　チラシ</v>
       </c>
       <c r="D118" t="str">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -6623,7 +6623,7 @@
         <v/>
       </c>
       <c r="H118" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -6632,10 +6632,10 @@
         <v/>
       </c>
       <c r="K118" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>チラシ</v>
       </c>
       <c r="L118" t="str">
-        <v>4550133504969</v>
+        <v>4550133464317</v>
       </c>
       <c r="M118" t="str">
         <v/>
@@ -6655,16 +6655,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>DLD10731</v>
+        <v>DLD10760</v>
       </c>
       <c r="B119" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C119" t="str">
-        <v>ＢＨマルチジグ８ｇ　ブラック</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　ブラック</v>
       </c>
       <c r="D119" t="str">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="H119" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -6688,7 +6688,7 @@
         <v>ブラック</v>
       </c>
       <c r="L119" t="str">
-        <v>4550133504976</v>
+        <v>4550133464324</v>
       </c>
       <c r="M119" t="str">
         <v/>
@@ -6708,16 +6708,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>DLD10732</v>
+        <v>DLD10761</v>
       </c>
       <c r="B120" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C120" t="str">
-        <v>ＢＨマルチジグ８ｇ　サマークロー</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　ヌマザリ</v>
       </c>
       <c r="D120" t="str">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -6729,7 +6729,7 @@
         <v/>
       </c>
       <c r="H120" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -6738,10 +6738,10 @@
         <v/>
       </c>
       <c r="K120" t="str">
-        <v>サマークロー</v>
+        <v>ヌマザリ</v>
       </c>
       <c r="L120" t="str">
-        <v>4550133504983</v>
+        <v>4550133464331</v>
       </c>
       <c r="M120" t="str">
         <v/>
@@ -6761,16 +6761,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>DLD10733</v>
+        <v>DLD10762</v>
       </c>
       <c r="B121" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C121" t="str">
-        <v>ＢＨマルチジグ８ｇ　マッディスペシャル</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　サマークロー</v>
       </c>
       <c r="D121" t="str">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -6782,7 +6782,7 @@
         <v/>
       </c>
       <c r="H121" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -6791,10 +6791,10 @@
         <v/>
       </c>
       <c r="K121" t="str">
-        <v>マッディスペシャル</v>
+        <v>サマークロー</v>
       </c>
       <c r="L121" t="str">
-        <v>4550133504990</v>
+        <v>4550133464348</v>
       </c>
       <c r="M121" t="str">
         <v/>
@@ -6814,16 +6814,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>DLD10734</v>
+        <v>DLD10763</v>
       </c>
       <c r="B122" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C122" t="str">
-        <v>ＢＨマルチジグ８ｇ　北産海老</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　ダークグリパンブルーフレーク</v>
       </c>
       <c r="D122" t="str">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -6835,7 +6835,7 @@
         <v/>
       </c>
       <c r="H122" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -6844,10 +6844,10 @@
         <v/>
       </c>
       <c r="K122" t="str">
-        <v>北産海老</v>
+        <v>ダークグリパンブルーフレーク</v>
       </c>
       <c r="L122" t="str">
-        <v>4550133505003</v>
+        <v>4550133464355</v>
       </c>
       <c r="M122" t="str">
         <v/>
@@ -6867,16 +6867,16 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>DLD10735</v>
+        <v>DLD10764</v>
       </c>
       <c r="B123" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C123" t="str">
-        <v>ＢＨマルチジグ８ｇ　キタサンホワイト</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　シュリンプ</v>
       </c>
       <c r="D123" t="str">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -6888,7 +6888,7 @@
         <v/>
       </c>
       <c r="H123" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -6897,10 +6897,10 @@
         <v/>
       </c>
       <c r="K123" t="str">
-        <v>キタサンホワイト</v>
+        <v>シュリンプ</v>
       </c>
       <c r="L123" t="str">
-        <v>4550133505010</v>
+        <v>4550133464362</v>
       </c>
       <c r="M123" t="str">
         <v/>
@@ -6920,16 +6920,16 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>DLD10736</v>
+        <v>DLD10765</v>
       </c>
       <c r="B124" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C124" t="str">
-        <v>ＢＨマルチジグ１０ｇ　グリーンパンプキン</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　パールスモーク</v>
       </c>
       <c r="D124" t="str">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -6941,7 +6941,7 @@
         <v/>
       </c>
       <c r="H124" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -6950,10 +6950,10 @@
         <v/>
       </c>
       <c r="K124" t="str">
-        <v>グリーンパンプキン</v>
+        <v>パールスモーク</v>
       </c>
       <c r="L124" t="str">
-        <v>4550133505027</v>
+        <v>4550133464379</v>
       </c>
       <c r="M124" t="str">
         <v/>
@@ -6973,16 +6973,16 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>DLD10737</v>
+        <v>DLD10766</v>
       </c>
       <c r="B125" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C125" t="str">
-        <v>ＢＨマルチジグ１０ｇ　グリパンピンク</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　グリーンパンプキンブルーＦＬ</v>
       </c>
       <c r="D125" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -6994,7 +6994,7 @@
         <v/>
       </c>
       <c r="H125" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -7003,10 +7003,10 @@
         <v/>
       </c>
       <c r="K125" t="str">
-        <v>グリパンピンク</v>
+        <v>グリーンパンプキンブルーＦＬ</v>
       </c>
       <c r="L125" t="str">
-        <v>4550133505034</v>
+        <v>4550133464386</v>
       </c>
       <c r="M125" t="str">
         <v/>
@@ -7026,16 +7026,16 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>DLD10738</v>
+        <v>DLD10767</v>
       </c>
       <c r="B126" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C126" t="str">
-        <v>ＢＨマルチジグ１０ｇ　テナガエビ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　チラシ</v>
       </c>
       <c r="D126" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -7047,7 +7047,7 @@
         <v/>
       </c>
       <c r="H126" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -7056,10 +7056,10 @@
         <v/>
       </c>
       <c r="K126" t="str">
-        <v>テナガエビ</v>
+        <v>チラシ</v>
       </c>
       <c r="L126" t="str">
-        <v>4550133505041</v>
+        <v>4550133464393</v>
       </c>
       <c r="M126" t="str">
         <v/>
@@ -7079,16 +7079,16 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>DLD10739</v>
+        <v>DLD10768</v>
       </c>
       <c r="B127" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C127" t="str">
-        <v>ＢＨマルチジグ１０ｇ　ゴリ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　ブラック</v>
       </c>
       <c r="D127" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -7100,7 +7100,7 @@
         <v/>
       </c>
       <c r="H127" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -7109,10 +7109,10 @@
         <v/>
       </c>
       <c r="K127" t="str">
-        <v>ゴリ</v>
+        <v>ブラック</v>
       </c>
       <c r="L127" t="str">
-        <v>4550133505058</v>
+        <v>4550133464409</v>
       </c>
       <c r="M127" t="str">
         <v/>
@@ -7132,16 +7132,16 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>DLD10740</v>
+        <v>DLD10769</v>
       </c>
       <c r="B128" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C128" t="str">
-        <v>ＢＨマルチジグ１０ｇ　沼ザリ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　ヌマザリ</v>
       </c>
       <c r="D128" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -7153,7 +7153,7 @@
         <v/>
       </c>
       <c r="H128" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -7162,10 +7162,10 @@
         <v/>
       </c>
       <c r="K128" t="str">
-        <v>沼ザリ</v>
+        <v>ヌマザリ</v>
       </c>
       <c r="L128" t="str">
-        <v>4550133505065</v>
+        <v>4550133464416</v>
       </c>
       <c r="M128" t="str">
         <v/>
@@ -7185,16 +7185,16 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>DLD10741</v>
+        <v>DLD10770</v>
       </c>
       <c r="B129" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C129" t="str">
-        <v>ＢＨマルチジグ１０ｇ　スポーンシュリンプ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　サマークロー</v>
       </c>
       <c r="D129" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -7206,7 +7206,7 @@
         <v/>
       </c>
       <c r="H129" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -7215,10 +7215,10 @@
         <v/>
       </c>
       <c r="K129" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>サマークロー</v>
       </c>
       <c r="L129" t="str">
-        <v>4550133505072</v>
+        <v>4550133464423</v>
       </c>
       <c r="M129" t="str">
         <v/>
@@ -7238,16 +7238,16 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>DLD10742</v>
+        <v>DLD10771</v>
       </c>
       <c r="B130" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C130" t="str">
-        <v>ＢＨマルチジグ１０ｇ　ブラック</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　ダークグリパンブルーフレーク</v>
       </c>
       <c r="D130" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -7259,7 +7259,7 @@
         <v/>
       </c>
       <c r="H130" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -7268,10 +7268,10 @@
         <v/>
       </c>
       <c r="K130" t="str">
-        <v>ブラック</v>
+        <v>ダークグリパンブルーフレーク</v>
       </c>
       <c r="L130" t="str">
-        <v>4550133505089</v>
+        <v>4550133464430</v>
       </c>
       <c r="M130" t="str">
         <v/>
@@ -7291,16 +7291,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>DLD10743</v>
+        <v>DLD10772</v>
       </c>
       <c r="B131" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C131" t="str">
-        <v>ＢＨマルチジグ１０ｇ　サマークロー</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　シュリンプ</v>
       </c>
       <c r="D131" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -7312,7 +7312,7 @@
         <v/>
       </c>
       <c r="H131" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -7321,10 +7321,10 @@
         <v/>
       </c>
       <c r="K131" t="str">
-        <v>サマークロー</v>
+        <v>シュリンプ</v>
       </c>
       <c r="L131" t="str">
-        <v>4550133505096</v>
+        <v>4550133464447</v>
       </c>
       <c r="M131" t="str">
         <v/>
@@ -7344,16 +7344,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>DLD10744</v>
+        <v>DLD10773</v>
       </c>
       <c r="B132" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C132" t="str">
-        <v>ＢＨマルチジグ１０ｇ　マッディスペシャル</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　パールスモーク</v>
       </c>
       <c r="D132" t="str">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -7365,7 +7365,7 @@
         <v/>
       </c>
       <c r="H132" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -7374,10 +7374,10 @@
         <v/>
       </c>
       <c r="K132" t="str">
-        <v>マッディスペシャル</v>
+        <v>パールスモーク</v>
       </c>
       <c r="L132" t="str">
-        <v>4550133505102</v>
+        <v>4550133464454</v>
       </c>
       <c r="M132" t="str">
         <v/>
@@ -7397,16 +7397,16 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>DLD10745</v>
+        <v>DLD10774</v>
       </c>
       <c r="B133" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C133" t="str">
-        <v>ＢＨマルチジグ１０ｇ　北産海老</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　グリーンパンプキンブルーＦＬ</v>
       </c>
       <c r="D133" t="str">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -7418,7 +7418,7 @@
         <v/>
       </c>
       <c r="H133" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -7427,10 +7427,10 @@
         <v/>
       </c>
       <c r="K133" t="str">
-        <v>北産海老</v>
+        <v>グリーンパンプキンブルーＦＬ</v>
       </c>
       <c r="L133" t="str">
-        <v>4550133505119</v>
+        <v>4550133464461</v>
       </c>
       <c r="M133" t="str">
         <v/>
@@ -7450,16 +7450,16 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>DLD10746</v>
+        <v>DLD10775</v>
       </c>
       <c r="B134" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C134" t="str">
-        <v>ＢＨマルチジグ１０ｇ　キタサンホワイト</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　チラシ</v>
       </c>
       <c r="D134" t="str">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -7471,7 +7471,7 @@
         <v/>
       </c>
       <c r="H134" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -7480,10 +7480,10 @@
         <v/>
       </c>
       <c r="K134" t="str">
-        <v>キタサンホワイト</v>
+        <v>チラシ</v>
       </c>
       <c r="L134" t="str">
-        <v>4550133505126</v>
+        <v>4550133464478</v>
       </c>
       <c r="M134" t="str">
         <v/>
@@ -7503,16 +7503,16 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>DLD10747</v>
+        <v>DLD10776</v>
       </c>
       <c r="B135" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C135" t="str">
-        <v>ＢＨマルチジグ１４ｇ　グリーンパンプキン</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　ブラック</v>
       </c>
       <c r="D135" t="str">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -7524,7 +7524,7 @@
         <v/>
       </c>
       <c r="H135" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -7533,10 +7533,10 @@
         <v/>
       </c>
       <c r="K135" t="str">
-        <v>グリーンパンプキン</v>
+        <v>ブラック</v>
       </c>
       <c r="L135" t="str">
-        <v>4550133505133</v>
+        <v>4550133464485</v>
       </c>
       <c r="M135" t="str">
         <v/>
@@ -7556,16 +7556,16 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>DLD10748</v>
+        <v>DLD10777</v>
       </c>
       <c r="B136" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C136" t="str">
-        <v>ＢＨマルチジグ１４ｇ　グリパンピンク</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　ヌマザリ</v>
       </c>
       <c r="D136" t="str">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -7577,7 +7577,7 @@
         <v/>
       </c>
       <c r="H136" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -7586,10 +7586,10 @@
         <v/>
       </c>
       <c r="K136" t="str">
-        <v>グリパンピンク</v>
+        <v>ヌマザリ</v>
       </c>
       <c r="L136" t="str">
-        <v>4550133505140</v>
+        <v>4550133464492</v>
       </c>
       <c r="M136" t="str">
         <v/>
@@ -7609,16 +7609,16 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>DLD10749</v>
+        <v>DLD10778</v>
       </c>
       <c r="B137" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C137" t="str">
-        <v>ＢＨマルチジグ１４ｇ　テナガエビ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　サマークロー</v>
       </c>
       <c r="D137" t="str">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -7630,7 +7630,7 @@
         <v/>
       </c>
       <c r="H137" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -7639,10 +7639,10 @@
         <v/>
       </c>
       <c r="K137" t="str">
-        <v>テナガエビ</v>
+        <v>サマークロー</v>
       </c>
       <c r="L137" t="str">
-        <v>4550133505157</v>
+        <v>4550133464508</v>
       </c>
       <c r="M137" t="str">
         <v/>
@@ -7662,16 +7662,16 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>DLD10750</v>
+        <v>DLD10779</v>
       </c>
       <c r="B138" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C138" t="str">
-        <v>ＢＨマルチジグ１４ｇ　ゴリ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　ダークグリパンブルーフレーク</v>
       </c>
       <c r="D138" t="str">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -7683,7 +7683,7 @@
         <v/>
       </c>
       <c r="H138" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -7692,10 +7692,10 @@
         <v/>
       </c>
       <c r="K138" t="str">
-        <v>ゴリ</v>
+        <v>ダークグリパンブルーフレーク</v>
       </c>
       <c r="L138" t="str">
-        <v>4550133505164</v>
+        <v>4550133464515</v>
       </c>
       <c r="M138" t="str">
         <v/>
@@ -7715,16 +7715,16 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>DLD10751</v>
+        <v>DLD10780</v>
       </c>
       <c r="B139" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C139" t="str">
-        <v>ＢＨマルチジグ１４ｇ　沼ザリ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　シュリンプ</v>
       </c>
       <c r="D139" t="str">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -7736,7 +7736,7 @@
         <v/>
       </c>
       <c r="H139" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -7745,10 +7745,10 @@
         <v/>
       </c>
       <c r="K139" t="str">
-        <v>沼ザリ</v>
+        <v>シュリンプ</v>
       </c>
       <c r="L139" t="str">
-        <v>4550133505171</v>
+        <v>4550133464522</v>
       </c>
       <c r="M139" t="str">
         <v/>
@@ -7768,16 +7768,16 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>DLD10752</v>
+        <v>DLD10781</v>
       </c>
       <c r="B140" t="str">
-        <v>DL1064</v>
+        <v>DL1065</v>
       </c>
       <c r="C140" t="str">
-        <v>ＢＨマルチジグ１４ｇ　スポーンシュリンプ</v>
+        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　パールスモーク</v>
       </c>
       <c r="D140" t="str">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -7789,7 +7789,7 @@
         <v/>
       </c>
       <c r="H140" t="str">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -7798,10 +7798,10 @@
         <v/>
       </c>
       <c r="K140" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>パールスモーク</v>
       </c>
       <c r="L140" t="str">
-        <v>4550133505188</v>
+        <v>4550133464539</v>
       </c>
       <c r="M140" t="str">
         <v/>
@@ -7821,16 +7821,16 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>DLD10753</v>
+        <v>DLD10782</v>
       </c>
       <c r="B141" t="str">
-        <v>DL1064</v>
+        <v>DL1066</v>
       </c>
       <c r="C141" t="str">
-        <v>ＢＨマルチジグ１４ｇ　ブラック</v>
+        <v>ＢＨジグスピナー３．５　ゴールドアユ</v>
       </c>
       <c r="D141" t="str">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -7842,7 +7842,7 @@
         <v/>
       </c>
       <c r="H141" t="str">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -7851,10 +7851,10 @@
         <v/>
       </c>
       <c r="K141" t="str">
-        <v>ブラック</v>
+        <v>ゴールドアユ</v>
       </c>
       <c r="L141" t="str">
-        <v>4550133505195</v>
+        <v>4550133508295</v>
       </c>
       <c r="M141" t="str">
         <v/>
@@ -7874,16 +7874,16 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>DLD10754</v>
+        <v>DLD10783</v>
       </c>
       <c r="B142" t="str">
-        <v>DL1064</v>
+        <v>DL1066</v>
       </c>
       <c r="C142" t="str">
-        <v>ＢＨマルチジグ１４ｇ　サマークロー</v>
+        <v>ＢＨジグスピナー３．５　ワカサギ</v>
       </c>
       <c r="D142" t="str">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
       <c r="H142" t="str">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -7904,10 +7904,10 @@
         <v/>
       </c>
       <c r="K142" t="str">
-        <v>サマークロー</v>
+        <v>ワカサギ</v>
       </c>
       <c r="L142" t="str">
-        <v>4550133505201</v>
+        <v>4550133508301</v>
       </c>
       <c r="M142" t="str">
         <v/>
@@ -7927,16 +7927,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>DLD10755</v>
+        <v>DLD10784</v>
       </c>
       <c r="B143" t="str">
-        <v>DL1064</v>
+        <v>DL1066</v>
       </c>
       <c r="C143" t="str">
-        <v>ＢＨマルチジグ１４ｇ　マッディスペシャル</v>
+        <v>ＢＨジグスピナー３．５　ブラウンシャッド</v>
       </c>
       <c r="D143" t="str">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -7948,7 +7948,7 @@
         <v/>
       </c>
       <c r="H143" t="str">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -7957,10 +7957,10 @@
         <v/>
       </c>
       <c r="K143" t="str">
-        <v>マッディスペシャル</v>
+        <v>ブラウンシャッド</v>
       </c>
       <c r="L143" t="str">
-        <v>4550133505218</v>
+        <v>4550133508318</v>
       </c>
       <c r="M143" t="str">
         <v/>
@@ -7980,16 +7980,16 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DLD10756</v>
+        <v>DLD10785</v>
       </c>
       <c r="B144" t="str">
-        <v>DL1064</v>
+        <v>DL1066</v>
       </c>
       <c r="C144" t="str">
-        <v>ＢＨマルチジグ１４ｇ　北産海老</v>
+        <v>ＢＨジグスピナー３．５　ブラック</v>
       </c>
       <c r="D144" t="str">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -8001,7 +8001,7 @@
         <v/>
       </c>
       <c r="H144" t="str">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -8010,10 +8010,10 @@
         <v/>
       </c>
       <c r="K144" t="str">
-        <v>北産海老</v>
+        <v>ブラック</v>
       </c>
       <c r="L144" t="str">
-        <v>4550133505225</v>
+        <v>4550133508325</v>
       </c>
       <c r="M144" t="str">
         <v/>
@@ -8033,16 +8033,16 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DLD10757</v>
+        <v>DLD10786</v>
       </c>
       <c r="B145" t="str">
-        <v>DL1064</v>
+        <v>DL1066</v>
       </c>
       <c r="C145" t="str">
-        <v>ＢＨマルチジグ１４ｇ　キタサンホワイト</v>
+        <v>ＢＨジグスピナー３．５　ブルーバックチャート</v>
       </c>
       <c r="D145" t="str">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -8054,7 +8054,7 @@
         <v/>
       </c>
       <c r="H145" t="str">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -8063,10 +8063,10 @@
         <v/>
       </c>
       <c r="K145" t="str">
-        <v>キタサンホワイト</v>
+        <v>ブルーバックチャート</v>
       </c>
       <c r="L145" t="str">
-        <v>4550133505232</v>
+        <v>4550133508332</v>
       </c>
       <c r="M145" t="str">
         <v/>
@@ -8086,16 +8086,16 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>DLD10758</v>
+        <v>DLD10787</v>
       </c>
       <c r="B146" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C146" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　グリーンパンプキンブルーＦＬ</v>
+        <v>ＢＨジグスピナー３．５　ホワイトシャッド</v>
       </c>
       <c r="D146" t="str">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -8107,7 +8107,7 @@
         <v/>
       </c>
       <c r="H146" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -8116,10 +8116,10 @@
         <v/>
       </c>
       <c r="K146" t="str">
-        <v>グリーンパンプキンブルーＦＬ</v>
+        <v>ホワイトシャッド</v>
       </c>
       <c r="L146" t="str">
-        <v>4550133464300</v>
+        <v>4550133508349</v>
       </c>
       <c r="M146" t="str">
         <v/>
@@ -8139,16 +8139,16 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DLD10759</v>
+        <v>DLD10788</v>
       </c>
       <c r="B147" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C147" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　チラシ</v>
+        <v>ＢＨジグスピナー５　ゴールドアユ</v>
       </c>
       <c r="D147" t="str">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -8160,7 +8160,7 @@
         <v/>
       </c>
       <c r="H147" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -8169,10 +8169,10 @@
         <v/>
       </c>
       <c r="K147" t="str">
-        <v>チラシ</v>
+        <v>ゴールドアユ</v>
       </c>
       <c r="L147" t="str">
-        <v>4550133464317</v>
+        <v>4550133508356</v>
       </c>
       <c r="M147" t="str">
         <v/>
@@ -8192,16 +8192,16 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>DLD10760</v>
+        <v>DLD10789</v>
       </c>
       <c r="B148" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C148" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　ブラック</v>
+        <v>ＢＨジグスピナー５　ワカサギ</v>
       </c>
       <c r="D148" t="str">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -8213,7 +8213,7 @@
         <v/>
       </c>
       <c r="H148" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -8222,10 +8222,10 @@
         <v/>
       </c>
       <c r="K148" t="str">
-        <v>ブラック</v>
+        <v>ワカサギ</v>
       </c>
       <c r="L148" t="str">
-        <v>4550133464324</v>
+        <v>4550133508363</v>
       </c>
       <c r="M148" t="str">
         <v/>
@@ -8245,16 +8245,16 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DLD10761</v>
+        <v>DLD10790</v>
       </c>
       <c r="B149" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C149" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　ヌマザリ</v>
+        <v>ＢＨジグスピナー５　ブラウンシャッド</v>
       </c>
       <c r="D149" t="str">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -8266,7 +8266,7 @@
         <v/>
       </c>
       <c r="H149" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -8275,10 +8275,10 @@
         <v/>
       </c>
       <c r="K149" t="str">
-        <v>ヌマザリ</v>
+        <v>ブラウンシャッド</v>
       </c>
       <c r="L149" t="str">
-        <v>4550133464331</v>
+        <v>4550133508370</v>
       </c>
       <c r="M149" t="str">
         <v/>
@@ -8298,16 +8298,16 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>DLD10762</v>
+        <v>DLD10791</v>
       </c>
       <c r="B150" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C150" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　サマークロー</v>
+        <v>ＢＨジグスピナー５　ブラック</v>
       </c>
       <c r="D150" t="str">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -8319,7 +8319,7 @@
         <v/>
       </c>
       <c r="H150" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -8328,10 +8328,10 @@
         <v/>
       </c>
       <c r="K150" t="str">
-        <v>サマークロー</v>
+        <v>ブラック</v>
       </c>
       <c r="L150" t="str">
-        <v>4550133464348</v>
+        <v>4550133508387</v>
       </c>
       <c r="M150" t="str">
         <v/>
@@ -8351,16 +8351,16 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>DLD10763</v>
+        <v>DLD10792</v>
       </c>
       <c r="B151" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C151" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　ダークグリパンブルーフレーク</v>
+        <v>ＢＨジグスピナー５　ブルーバックチャート</v>
       </c>
       <c r="D151" t="str">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -8372,7 +8372,7 @@
         <v/>
       </c>
       <c r="H151" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -8381,10 +8381,10 @@
         <v/>
       </c>
       <c r="K151" t="str">
-        <v>ダークグリパンブルーフレーク</v>
+        <v>ブルーバックチャート</v>
       </c>
       <c r="L151" t="str">
-        <v>4550133464355</v>
+        <v>4550133508394</v>
       </c>
       <c r="M151" t="str">
         <v/>
@@ -8404,16 +8404,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>DLD10764</v>
+        <v>DLD10793</v>
       </c>
       <c r="B152" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C152" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　シュリンプ</v>
+        <v>ＢＨジグスピナー５　ホワイトシャッド</v>
       </c>
       <c r="D152" t="str">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -8425,7 +8425,7 @@
         <v/>
       </c>
       <c r="H152" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -8434,10 +8434,10 @@
         <v/>
       </c>
       <c r="K152" t="str">
-        <v>シュリンプ</v>
+        <v>ホワイトシャッド</v>
       </c>
       <c r="L152" t="str">
-        <v>4550133464362</v>
+        <v>4550133508400</v>
       </c>
       <c r="M152" t="str">
         <v/>
@@ -8457,16 +8457,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>DLD10765</v>
+        <v>DLD10794</v>
       </c>
       <c r="B153" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C153" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー２．７ｇ　パールスモーク</v>
+        <v>ＢＨジグスピナー７　ゴールドアユ</v>
       </c>
       <c r="D153" t="str">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -8478,7 +8478,7 @@
         <v/>
       </c>
       <c r="H153" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -8487,10 +8487,10 @@
         <v/>
       </c>
       <c r="K153" t="str">
-        <v>パールスモーク</v>
+        <v>ゴールドアユ</v>
       </c>
       <c r="L153" t="str">
-        <v>4550133464379</v>
+        <v>4550133508417</v>
       </c>
       <c r="M153" t="str">
         <v/>
@@ -8510,16 +8510,16 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>DLD10766</v>
+        <v>DLD10795</v>
       </c>
       <c r="B154" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C154" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　グリーンパンプキンブルーＦＬ</v>
+        <v>ＢＨジグスピナー７　ワカサギ</v>
       </c>
       <c r="D154" t="str">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -8531,7 +8531,7 @@
         <v/>
       </c>
       <c r="H154" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -8540,10 +8540,10 @@
         <v/>
       </c>
       <c r="K154" t="str">
-        <v>グリーンパンプキンブルーＦＬ</v>
+        <v>ワカサギ</v>
       </c>
       <c r="L154" t="str">
-        <v>4550133464386</v>
+        <v>4550133508424</v>
       </c>
       <c r="M154" t="str">
         <v/>
@@ -8563,16 +8563,16 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>DLD10767</v>
+        <v>DLD10796</v>
       </c>
       <c r="B155" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C155" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　チラシ</v>
+        <v>ＢＨジグスピナー７　ブラウンシャッド</v>
       </c>
       <c r="D155" t="str">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -8584,7 +8584,7 @@
         <v/>
       </c>
       <c r="H155" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -8593,10 +8593,10 @@
         <v/>
       </c>
       <c r="K155" t="str">
-        <v>チラシ</v>
+        <v>ブラウンシャッド</v>
       </c>
       <c r="L155" t="str">
-        <v>4550133464393</v>
+        <v>4550133508431</v>
       </c>
       <c r="M155" t="str">
         <v/>
@@ -8616,16 +8616,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>DLD10768</v>
+        <v>DLD10797</v>
       </c>
       <c r="B156" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C156" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　ブラック</v>
+        <v>ＢＨジグスピナー７　ブラック</v>
       </c>
       <c r="D156" t="str">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -8637,7 +8637,7 @@
         <v/>
       </c>
       <c r="H156" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -8649,7 +8649,7 @@
         <v>ブラック</v>
       </c>
       <c r="L156" t="str">
-        <v>4550133464409</v>
+        <v>4550133508448</v>
       </c>
       <c r="M156" t="str">
         <v/>
@@ -8669,16 +8669,16 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>DLD10769</v>
+        <v>DLD10798</v>
       </c>
       <c r="B157" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C157" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　ヌマザリ</v>
+        <v>ＢＨジグスピナー７　ブルーバックチャート</v>
       </c>
       <c r="D157" t="str">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -8690,7 +8690,7 @@
         <v/>
       </c>
       <c r="H157" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I157" t="str">
         <v/>
@@ -8699,10 +8699,10 @@
         <v/>
       </c>
       <c r="K157" t="str">
-        <v>ヌマザリ</v>
+        <v>ブルーバックチャート</v>
       </c>
       <c r="L157" t="str">
-        <v>4550133464416</v>
+        <v>4550133508455</v>
       </c>
       <c r="M157" t="str">
         <v/>
@@ -8722,16 +8722,16 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>DLD10770</v>
+        <v>DLD10799</v>
       </c>
       <c r="B158" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C158" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　サマークロー</v>
+        <v>ＢＨジグスピナー７　ホワイトシャッド</v>
       </c>
       <c r="D158" t="str">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -8743,7 +8743,7 @@
         <v/>
       </c>
       <c r="H158" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -8752,10 +8752,10 @@
         <v/>
       </c>
       <c r="K158" t="str">
-        <v>サマークロー</v>
+        <v>ホワイトシャッド</v>
       </c>
       <c r="L158" t="str">
-        <v>4550133464423</v>
+        <v>4550133508462</v>
       </c>
       <c r="M158" t="str">
         <v/>
@@ -8775,16 +8775,16 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>DLD10771</v>
+        <v>DLD10800</v>
       </c>
       <c r="B159" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C159" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　ダークグリパンブルーフレーク</v>
+        <v>ＢＨジグスピナー１０　ゴールドアユ</v>
       </c>
       <c r="D159" t="str">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -8796,7 +8796,7 @@
         <v/>
       </c>
       <c r="H159" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -8805,10 +8805,10 @@
         <v/>
       </c>
       <c r="K159" t="str">
-        <v>ダークグリパンブルーフレーク</v>
+        <v>ゴールドアユ</v>
       </c>
       <c r="L159" t="str">
-        <v>4550133464430</v>
+        <v>4550133508479</v>
       </c>
       <c r="M159" t="str">
         <v/>
@@ -8828,16 +8828,16 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DLD10772</v>
+        <v>DLD10801</v>
       </c>
       <c r="B160" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C160" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　シュリンプ</v>
+        <v>ＢＨジグスピナー１０　ワカサギ</v>
       </c>
       <c r="D160" t="str">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -8849,7 +8849,7 @@
         <v/>
       </c>
       <c r="H160" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -8858,10 +8858,10 @@
         <v/>
       </c>
       <c r="K160" t="str">
-        <v>シュリンプ</v>
+        <v>ワカサギ</v>
       </c>
       <c r="L160" t="str">
-        <v>4550133464447</v>
+        <v>4550133508486</v>
       </c>
       <c r="M160" t="str">
         <v/>
@@ -8881,16 +8881,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>DLD10773</v>
+        <v>DLD10802</v>
       </c>
       <c r="B161" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C161" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー３．５ｇ　パールスモーク</v>
+        <v>ＢＨジグスピナー１０　ブラウンシャッド</v>
       </c>
       <c r="D161" t="str">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -8902,7 +8902,7 @@
         <v/>
       </c>
       <c r="H161" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -8911,10 +8911,10 @@
         <v/>
       </c>
       <c r="K161" t="str">
-        <v>パールスモーク</v>
+        <v>ブラウンシャッド</v>
       </c>
       <c r="L161" t="str">
-        <v>4550133464454</v>
+        <v>4550133508493</v>
       </c>
       <c r="M161" t="str">
         <v/>
@@ -8934,16 +8934,16 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>DLD10774</v>
+        <v>DLD10803</v>
       </c>
       <c r="B162" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C162" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　グリーンパンプキンブルーＦＬ</v>
+        <v>ＢＨジグスピナー１０　ブラック</v>
       </c>
       <c r="D162" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -8955,7 +8955,7 @@
         <v/>
       </c>
       <c r="H162" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I162" t="str">
         <v/>
@@ -8964,10 +8964,10 @@
         <v/>
       </c>
       <c r="K162" t="str">
-        <v>グリーンパンプキンブルーＦＬ</v>
+        <v>ブラック</v>
       </c>
       <c r="L162" t="str">
-        <v>4550133464461</v>
+        <v>4550133508509</v>
       </c>
       <c r="M162" t="str">
         <v/>
@@ -8987,16 +8987,16 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>DLD10775</v>
+        <v>DLD10804</v>
       </c>
       <c r="B163" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C163" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　チラシ</v>
+        <v>ＢＨジグスピナー１０　ブルーバックチャート</v>
       </c>
       <c r="D163" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -9008,7 +9008,7 @@
         <v/>
       </c>
       <c r="H163" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -9017,10 +9017,10 @@
         <v/>
       </c>
       <c r="K163" t="str">
-        <v>チラシ</v>
+        <v>ブルーバックチャート</v>
       </c>
       <c r="L163" t="str">
-        <v>4550133464478</v>
+        <v>4550133508516</v>
       </c>
       <c r="M163" t="str">
         <v/>
@@ -9040,16 +9040,16 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>DLD10776</v>
+        <v>DLD10805</v>
       </c>
       <c r="B164" t="str">
-        <v>DL1065</v>
+        <v>DL1066</v>
       </c>
       <c r="C164" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　ブラック</v>
+        <v>ＢＨジグスピナー１０　ホワイトシャッド</v>
       </c>
       <c r="D164" t="str">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -9061,7 +9061,7 @@
         <v/>
       </c>
       <c r="H164" t="str">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -9070,10 +9070,10 @@
         <v/>
       </c>
       <c r="K164" t="str">
-        <v>ブラック</v>
+        <v>ホワイトシャッド</v>
       </c>
       <c r="L164" t="str">
-        <v>4550133464485</v>
+        <v>4550133508523</v>
       </c>
       <c r="M164" t="str">
         <v/>
@@ -9093,16 +9093,16 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>DLD10777</v>
+        <v>DLD10806</v>
       </c>
       <c r="B165" t="str">
-        <v>DL1065</v>
+        <v>DL1067</v>
       </c>
       <c r="C165" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　ヌマザリ</v>
+        <v>ＢＨミニジグ１．３ｇ　グリーンパンプキン</v>
       </c>
       <c r="D165" t="str">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -9114,7 +9114,7 @@
         <v/>
       </c>
       <c r="H165" t="str">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -9123,10 +9123,10 @@
         <v/>
       </c>
       <c r="K165" t="str">
-        <v>ヌマザリ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L165" t="str">
-        <v>4550133464492</v>
+        <v>4550133505515</v>
       </c>
       <c r="M165" t="str">
         <v/>
@@ -9146,16 +9146,16 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>DLD10778</v>
+        <v>DLD10807</v>
       </c>
       <c r="B166" t="str">
-        <v>DL1065</v>
+        <v>DL1067</v>
       </c>
       <c r="C166" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　サマークロー</v>
+        <v>ＢＨミニジグ１．３ｇ　ゴールドスジエビ</v>
       </c>
       <c r="D166" t="str">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -9167,7 +9167,7 @@
         <v/>
       </c>
       <c r="H166" t="str">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -9176,10 +9176,10 @@
         <v/>
       </c>
       <c r="K166" t="str">
-        <v>サマークロー</v>
+        <v>ゴールドスジエビ</v>
       </c>
       <c r="L166" t="str">
-        <v>4550133464508</v>
+        <v>4550133505522</v>
       </c>
       <c r="M166" t="str">
         <v/>
@@ -9199,16 +9199,16 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>DLD10779</v>
+        <v>DLD10808</v>
       </c>
       <c r="B167" t="str">
-        <v>DL1065</v>
+        <v>DL1067</v>
       </c>
       <c r="C167" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　ダークグリパンブルーフレーク</v>
+        <v>ＢＨミニジグ１．３ｇ　グリパンピンク</v>
       </c>
       <c r="D167" t="str">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -9220,7 +9220,7 @@
         <v/>
       </c>
       <c r="H167" t="str">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -9229,10 +9229,10 @@
         <v/>
       </c>
       <c r="K167" t="str">
-        <v>ダークグリパンブルーフレーク</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L167" t="str">
-        <v>4550133464515</v>
+        <v>4550133505539</v>
       </c>
       <c r="M167" t="str">
         <v/>
@@ -9252,16 +9252,16 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>DLD10780</v>
+        <v>DLD10809</v>
       </c>
       <c r="B168" t="str">
-        <v>DL1065</v>
+        <v>DL1067</v>
       </c>
       <c r="C168" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　シュリンプ</v>
+        <v>ＢＨミニジグ１．３ｇ　テナガエビ</v>
       </c>
       <c r="D168" t="str">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -9273,7 +9273,7 @@
         <v/>
       </c>
       <c r="H168" t="str">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -9282,10 +9282,10 @@
         <v/>
       </c>
       <c r="K168" t="str">
-        <v>シュリンプ</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L168" t="str">
-        <v>4550133464522</v>
+        <v>4550133505546</v>
       </c>
       <c r="M168" t="str">
         <v/>
@@ -9305,16 +9305,16 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>DLD10781</v>
+        <v>DLD10810</v>
       </c>
       <c r="B169" t="str">
-        <v>DL1065</v>
+        <v>DL1067</v>
       </c>
       <c r="C169" t="str">
-        <v>ＳＴＥＥＺパワーフィネスジグＴｙｐｅカバー４．７ｇ　パールスモーク</v>
+        <v>ＢＨミニジグ１．３ｇ　クリスタルシュリンプ</v>
       </c>
       <c r="D169" t="str">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -9326,7 +9326,7 @@
         <v/>
       </c>
       <c r="H169" t="str">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -9335,10 +9335,10 @@
         <v/>
       </c>
       <c r="K169" t="str">
-        <v>パールスモーク</v>
+        <v>クリスタルシュリンプ</v>
       </c>
       <c r="L169" t="str">
-        <v>4550133464539</v>
+        <v>4550133505553</v>
       </c>
       <c r="M169" t="str">
         <v/>
@@ -9358,16 +9358,16 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>DLD10782</v>
+        <v>DLD10811</v>
       </c>
       <c r="B170" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C170" t="str">
-        <v>ＢＨジグスピナー３．５　ゴールドアユ</v>
+        <v>ＢＨミニジグ１．３ｇ　ゴリ</v>
       </c>
       <c r="D170" t="str">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -9379,7 +9379,7 @@
         <v/>
       </c>
       <c r="H170" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I170" t="str">
         <v/>
@@ -9388,10 +9388,10 @@
         <v/>
       </c>
       <c r="K170" t="str">
-        <v>ゴールドアユ</v>
+        <v>ゴリ</v>
       </c>
       <c r="L170" t="str">
-        <v>4550133508295</v>
+        <v>4550133505560</v>
       </c>
       <c r="M170" t="str">
         <v/>
@@ -9411,16 +9411,16 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>DLD10783</v>
+        <v>DLD10812</v>
       </c>
       <c r="B171" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C171" t="str">
-        <v>ＢＨジグスピナー３．５　ワカサギ</v>
+        <v>ＢＨミニジグ１．３ｇ　沼ザリ</v>
       </c>
       <c r="D171" t="str">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -9432,7 +9432,7 @@
         <v/>
       </c>
       <c r="H171" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -9441,10 +9441,10 @@
         <v/>
       </c>
       <c r="K171" t="str">
-        <v>ワカサギ</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L171" t="str">
-        <v>4550133508301</v>
+        <v>4550133505577</v>
       </c>
       <c r="M171" t="str">
         <v/>
@@ -9464,16 +9464,16 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>DLD10784</v>
+        <v>DLD10813</v>
       </c>
       <c r="B172" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C172" t="str">
-        <v>ＢＨジグスピナー３．５　ブラウンシャッド</v>
+        <v>ＢＨミニジグ１．３ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D172" t="str">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -9485,7 +9485,7 @@
         <v/>
       </c>
       <c r="H172" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -9494,10 +9494,10 @@
         <v/>
       </c>
       <c r="K172" t="str">
-        <v>ブラウンシャッド</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L172" t="str">
-        <v>4550133508318</v>
+        <v>4550133505584</v>
       </c>
       <c r="M172" t="str">
         <v/>
@@ -9517,16 +9517,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>DLD10785</v>
+        <v>DLD10814</v>
       </c>
       <c r="B173" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C173" t="str">
-        <v>ＢＨジグスピナー３．５　ブラック</v>
+        <v>ＢＨミニジグ１．３ｇ　ブラック</v>
       </c>
       <c r="D173" t="str">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -9538,7 +9538,7 @@
         <v/>
       </c>
       <c r="H173" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I173" t="str">
         <v/>
@@ -9550,7 +9550,7 @@
         <v>ブラック</v>
       </c>
       <c r="L173" t="str">
-        <v>4550133508325</v>
+        <v>4550133505591</v>
       </c>
       <c r="M173" t="str">
         <v/>
@@ -9570,16 +9570,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>DLD10786</v>
+        <v>DLD10815</v>
       </c>
       <c r="B174" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C174" t="str">
-        <v>ＢＨジグスピナー３．５　ブルーバックチャート</v>
+        <v>ＢＨミニジグ１．３ｇ　サマークロー</v>
       </c>
       <c r="D174" t="str">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -9591,7 +9591,7 @@
         <v/>
       </c>
       <c r="H174" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -9600,10 +9600,10 @@
         <v/>
       </c>
       <c r="K174" t="str">
-        <v>ブルーバックチャート</v>
+        <v>サマークロー</v>
       </c>
       <c r="L174" t="str">
-        <v>4550133508332</v>
+        <v>4550133505607</v>
       </c>
       <c r="M174" t="str">
         <v/>
@@ -9623,16 +9623,16 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>DLD10787</v>
+        <v>DLD10816</v>
       </c>
       <c r="B175" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C175" t="str">
-        <v>ＢＨジグスピナー３．５　ホワイトシャッド</v>
+        <v>ＢＨミニジグ１．８ｇ　グリーンパンプキン</v>
       </c>
       <c r="D175" t="str">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -9644,7 +9644,7 @@
         <v/>
       </c>
       <c r="H175" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -9653,10 +9653,10 @@
         <v/>
       </c>
       <c r="K175" t="str">
-        <v>ホワイトシャッド</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L175" t="str">
-        <v>4550133508349</v>
+        <v>4550133505614</v>
       </c>
       <c r="M175" t="str">
         <v/>
@@ -9676,16 +9676,16 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>DLD10788</v>
+        <v>DLD10817</v>
       </c>
       <c r="B176" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C176" t="str">
-        <v>ＢＨジグスピナー５　ゴールドアユ</v>
+        <v>ＢＨミニジグ１．８ｇ　ゴールドスジエビ</v>
       </c>
       <c r="D176" t="str">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -9697,7 +9697,7 @@
         <v/>
       </c>
       <c r="H176" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -9706,10 +9706,10 @@
         <v/>
       </c>
       <c r="K176" t="str">
-        <v>ゴールドアユ</v>
+        <v>ゴールドスジエビ</v>
       </c>
       <c r="L176" t="str">
-        <v>4550133508356</v>
+        <v>4550133505621</v>
       </c>
       <c r="M176" t="str">
         <v/>
@@ -9729,16 +9729,16 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>DLD10789</v>
+        <v>DLD10818</v>
       </c>
       <c r="B177" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C177" t="str">
-        <v>ＢＨジグスピナー５　ワカサギ</v>
+        <v>ＢＨミニジグ１．８ｇ　グリパンピンク</v>
       </c>
       <c r="D177" t="str">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -9750,7 +9750,7 @@
         <v/>
       </c>
       <c r="H177" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -9759,10 +9759,10 @@
         <v/>
       </c>
       <c r="K177" t="str">
-        <v>ワカサギ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L177" t="str">
-        <v>4550133508363</v>
+        <v>4550133505638</v>
       </c>
       <c r="M177" t="str">
         <v/>
@@ -9782,16 +9782,16 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>DLD10790</v>
+        <v>DLD10819</v>
       </c>
       <c r="B178" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C178" t="str">
-        <v>ＢＨジグスピナー５　ブラウンシャッド</v>
+        <v>ＢＨミニジグ１．８ｇ　テナガエビ</v>
       </c>
       <c r="D178" t="str">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -9803,7 +9803,7 @@
         <v/>
       </c>
       <c r="H178" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -9812,10 +9812,10 @@
         <v/>
       </c>
       <c r="K178" t="str">
-        <v>ブラウンシャッド</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L178" t="str">
-        <v>4550133508370</v>
+        <v>4550133505645</v>
       </c>
       <c r="M178" t="str">
         <v/>
@@ -9835,16 +9835,16 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>DLD10791</v>
+        <v>DLD10820</v>
       </c>
       <c r="B179" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C179" t="str">
-        <v>ＢＨジグスピナー５　ブラック</v>
+        <v>ＢＨミニジグ１．８ｇ　クリスタルシュリンプ</v>
       </c>
       <c r="D179" t="str">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -9856,7 +9856,7 @@
         <v/>
       </c>
       <c r="H179" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -9865,10 +9865,10 @@
         <v/>
       </c>
       <c r="K179" t="str">
-        <v>ブラック</v>
+        <v>クリスタルシュリンプ</v>
       </c>
       <c r="L179" t="str">
-        <v>4550133508387</v>
+        <v>4550133505652</v>
       </c>
       <c r="M179" t="str">
         <v/>
@@ -9888,16 +9888,16 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>DLD10792</v>
+        <v>DLD10821</v>
       </c>
       <c r="B180" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C180" t="str">
-        <v>ＢＨジグスピナー５　ブルーバックチャート</v>
+        <v>ＢＨミニジグ１．８ｇ　ゴリ</v>
       </c>
       <c r="D180" t="str">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -9909,7 +9909,7 @@
         <v/>
       </c>
       <c r="H180" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -9918,10 +9918,10 @@
         <v/>
       </c>
       <c r="K180" t="str">
-        <v>ブルーバックチャート</v>
+        <v>ゴリ</v>
       </c>
       <c r="L180" t="str">
-        <v>4550133508394</v>
+        <v>4550133505669</v>
       </c>
       <c r="M180" t="str">
         <v/>
@@ -9941,16 +9941,16 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>DLD10793</v>
+        <v>DLD10822</v>
       </c>
       <c r="B181" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C181" t="str">
-        <v>ＢＨジグスピナー５　ホワイトシャッド</v>
+        <v>ＢＨミニジグ１．８ｇ　沼ザリ</v>
       </c>
       <c r="D181" t="str">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -9962,7 +9962,7 @@
         <v/>
       </c>
       <c r="H181" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -9971,10 +9971,10 @@
         <v/>
       </c>
       <c r="K181" t="str">
-        <v>ホワイトシャッド</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L181" t="str">
-        <v>4550133508400</v>
+        <v>4550133505676</v>
       </c>
       <c r="M181" t="str">
         <v/>
@@ -9994,16 +9994,16 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>DLD10794</v>
+        <v>DLD10823</v>
       </c>
       <c r="B182" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C182" t="str">
-        <v>ＢＨジグスピナー７　ゴールドアユ</v>
+        <v>ＢＨミニジグ１．８ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D182" t="str">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -10015,7 +10015,7 @@
         <v/>
       </c>
       <c r="H182" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -10024,10 +10024,10 @@
         <v/>
       </c>
       <c r="K182" t="str">
-        <v>ゴールドアユ</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L182" t="str">
-        <v>4550133508417</v>
+        <v>4550133505683</v>
       </c>
       <c r="M182" t="str">
         <v/>
@@ -10047,16 +10047,16 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>DLD10795</v>
+        <v>DLD10824</v>
       </c>
       <c r="B183" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C183" t="str">
-        <v>ＢＨジグスピナー７　ワカサギ</v>
+        <v>ＢＨミニジグ１．８ｇ　ブラック</v>
       </c>
       <c r="D183" t="str">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -10068,7 +10068,7 @@
         <v/>
       </c>
       <c r="H183" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -10077,10 +10077,10 @@
         <v/>
       </c>
       <c r="K183" t="str">
-        <v>ワカサギ</v>
+        <v>ブラック</v>
       </c>
       <c r="L183" t="str">
-        <v>4550133508424</v>
+        <v>4550133505690</v>
       </c>
       <c r="M183" t="str">
         <v/>
@@ -10100,16 +10100,16 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>DLD10796</v>
+        <v>DLD10825</v>
       </c>
       <c r="B184" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C184" t="str">
-        <v>ＢＨジグスピナー７　ブラウンシャッド</v>
+        <v>ＢＨミニジグ１．８ｇ　サマークロー</v>
       </c>
       <c r="D184" t="str">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -10121,7 +10121,7 @@
         <v/>
       </c>
       <c r="H184" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -10130,10 +10130,10 @@
         <v/>
       </c>
       <c r="K184" t="str">
-        <v>ブラウンシャッド</v>
+        <v>サマークロー</v>
       </c>
       <c r="L184" t="str">
-        <v>4550133508431</v>
+        <v>4550133505706</v>
       </c>
       <c r="M184" t="str">
         <v/>
@@ -10153,16 +10153,16 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>DLD10797</v>
+        <v>DLD10826</v>
       </c>
       <c r="B185" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C185" t="str">
-        <v>ＢＨジグスピナー７　ブラック</v>
+        <v>ＢＨミニジグ２．５ｇ　グリーンパンプキン</v>
       </c>
       <c r="D185" t="str">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -10174,7 +10174,7 @@
         <v/>
       </c>
       <c r="H185" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -10183,10 +10183,10 @@
         <v/>
       </c>
       <c r="K185" t="str">
-        <v>ブラック</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L185" t="str">
-        <v>4550133508448</v>
+        <v>4550133505713</v>
       </c>
       <c r="M185" t="str">
         <v/>
@@ -10206,16 +10206,16 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DLD10798</v>
+        <v>DLD10827</v>
       </c>
       <c r="B186" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C186" t="str">
-        <v>ＢＨジグスピナー７　ブルーバックチャート</v>
+        <v>ＢＨミニジグ２．５ｇ　ゴールドスジエビ</v>
       </c>
       <c r="D186" t="str">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -10227,7 +10227,7 @@
         <v/>
       </c>
       <c r="H186" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -10236,10 +10236,10 @@
         <v/>
       </c>
       <c r="K186" t="str">
-        <v>ブルーバックチャート</v>
+        <v>ゴールドスジエビ</v>
       </c>
       <c r="L186" t="str">
-        <v>4550133508455</v>
+        <v>4550133505720</v>
       </c>
       <c r="M186" t="str">
         <v/>
@@ -10259,16 +10259,16 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DLD10799</v>
+        <v>DLD10828</v>
       </c>
       <c r="B187" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C187" t="str">
-        <v>ＢＨジグスピナー７　ホワイトシャッド</v>
+        <v>ＢＨミニジグ２．５ｇ　グリパンピンク</v>
       </c>
       <c r="D187" t="str">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -10280,7 +10280,7 @@
         <v/>
       </c>
       <c r="H187" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -10289,10 +10289,10 @@
         <v/>
       </c>
       <c r="K187" t="str">
-        <v>ホワイトシャッド</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L187" t="str">
-        <v>4550133508462</v>
+        <v>4550133505737</v>
       </c>
       <c r="M187" t="str">
         <v/>
@@ -10312,16 +10312,16 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>DLD10800</v>
+        <v>DLD10829</v>
       </c>
       <c r="B188" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C188" t="str">
-        <v>ＢＨジグスピナー１０　ゴールドアユ</v>
+        <v>ＢＨミニジグ２．５ｇ　テナガエビ</v>
       </c>
       <c r="D188" t="str">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -10333,7 +10333,7 @@
         <v/>
       </c>
       <c r="H188" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -10342,10 +10342,10 @@
         <v/>
       </c>
       <c r="K188" t="str">
-        <v>ゴールドアユ</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L188" t="str">
-        <v>4550133508479</v>
+        <v>4550133505744</v>
       </c>
       <c r="M188" t="str">
         <v/>
@@ -10365,16 +10365,16 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DLD10801</v>
+        <v>DLD10830</v>
       </c>
       <c r="B189" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C189" t="str">
-        <v>ＢＨジグスピナー１０　ワカサギ</v>
+        <v>ＢＨミニジグ２．５ｇ　クリスタルシュリンプ</v>
       </c>
       <c r="D189" t="str">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
         <v/>
       </c>
       <c r="H189" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -10395,10 +10395,10 @@
         <v/>
       </c>
       <c r="K189" t="str">
-        <v>ワカサギ</v>
+        <v>クリスタルシュリンプ</v>
       </c>
       <c r="L189" t="str">
-        <v>4550133508486</v>
+        <v>4550133505751</v>
       </c>
       <c r="M189" t="str">
         <v/>
@@ -10418,16 +10418,16 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>DLD10802</v>
+        <v>DLD10831</v>
       </c>
       <c r="B190" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C190" t="str">
-        <v>ＢＨジグスピナー１０　ブラウンシャッド</v>
+        <v>ＢＨミニジグ２．５ｇ　ゴリ</v>
       </c>
       <c r="D190" t="str">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -10439,7 +10439,7 @@
         <v/>
       </c>
       <c r="H190" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I190" t="str">
         <v/>
@@ -10448,10 +10448,10 @@
         <v/>
       </c>
       <c r="K190" t="str">
-        <v>ブラウンシャッド</v>
+        <v>ゴリ</v>
       </c>
       <c r="L190" t="str">
-        <v>4550133508493</v>
+        <v>4550133505768</v>
       </c>
       <c r="M190" t="str">
         <v/>
@@ -10471,16 +10471,16 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DLD10803</v>
+        <v>DLD10832</v>
       </c>
       <c r="B191" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C191" t="str">
-        <v>ＢＨジグスピナー１０　ブラック</v>
+        <v>ＢＨミニジグ２．５ｇ　沼ザリ</v>
       </c>
       <c r="D191" t="str">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -10492,7 +10492,7 @@
         <v/>
       </c>
       <c r="H191" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I191" t="str">
         <v/>
@@ -10501,10 +10501,10 @@
         <v/>
       </c>
       <c r="K191" t="str">
-        <v>ブラック</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L191" t="str">
-        <v>4550133508509</v>
+        <v>4550133505775</v>
       </c>
       <c r="M191" t="str">
         <v/>
@@ -10524,16 +10524,16 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>DLD10804</v>
+        <v>DLD10833</v>
       </c>
       <c r="B192" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C192" t="str">
-        <v>ＢＨジグスピナー１０　ブルーバックチャート</v>
+        <v>ＢＨミニジグ２．５ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D192" t="str">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -10545,7 +10545,7 @@
         <v/>
       </c>
       <c r="H192" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -10554,10 +10554,10 @@
         <v/>
       </c>
       <c r="K192" t="str">
-        <v>ブルーバックチャート</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L192" t="str">
-        <v>4550133508516</v>
+        <v>4550133505782</v>
       </c>
       <c r="M192" t="str">
         <v/>
@@ -10577,16 +10577,16 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>DLD10805</v>
+        <v>DLD10834</v>
       </c>
       <c r="B193" t="str">
-        <v>DL1066</v>
+        <v>DL1067</v>
       </c>
       <c r="C193" t="str">
-        <v>ＢＨジグスピナー１０　ホワイトシャッド</v>
+        <v>ＢＨミニジグ２．５ｇ　ブラック</v>
       </c>
       <c r="D193" t="str">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -10598,7 +10598,7 @@
         <v/>
       </c>
       <c r="H193" t="str">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -10607,10 +10607,10 @@
         <v/>
       </c>
       <c r="K193" t="str">
-        <v>ホワイトシャッド</v>
+        <v>ブラック</v>
       </c>
       <c r="L193" t="str">
-        <v>4550133508523</v>
+        <v>4550133505799</v>
       </c>
       <c r="M193" t="str">
         <v/>
@@ -10630,16 +10630,16 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>DLD10806</v>
+        <v>DLD10835</v>
       </c>
       <c r="B194" t="str">
         <v>DL1067</v>
       </c>
       <c r="C194" t="str">
-        <v>ＢＨミニジグ１．３ｇ　グリーンパンプキン</v>
+        <v>ＢＨミニジグ２．５ｇ　サマークロー</v>
       </c>
       <c r="D194" t="str">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -10660,10 +10660,10 @@
         <v/>
       </c>
       <c r="K194" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L194" t="str">
-        <v>4550133505515</v>
+        <v>4550133505805</v>
       </c>
       <c r="M194" t="str">
         <v/>
@@ -10683,16 +10683,16 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>DLD10807</v>
+        <v>DLD10836</v>
       </c>
       <c r="B195" t="str">
         <v>DL1067</v>
       </c>
       <c r="C195" t="str">
-        <v>ＢＨミニジグ１．３ｇ　ゴールドスジエビ</v>
+        <v>ＢＨミニジグ３．２ｇ　グリーンパンプキン</v>
       </c>
       <c r="D195" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -10713,10 +10713,10 @@
         <v/>
       </c>
       <c r="K195" t="str">
-        <v>ゴールドスジエビ</v>
+        <v>グリーンパンプキン</v>
       </c>
       <c r="L195" t="str">
-        <v>4550133505522</v>
+        <v>4550133505812</v>
       </c>
       <c r="M195" t="str">
         <v/>
@@ -10736,16 +10736,16 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>DLD10808</v>
+        <v>DLD10837</v>
       </c>
       <c r="B196" t="str">
         <v>DL1067</v>
       </c>
       <c r="C196" t="str">
-        <v>ＢＨミニジグ１．３ｇ　グリパンピンク</v>
+        <v>ＢＨミニジグ３．２ｇ　ゴールドスジエビ</v>
       </c>
       <c r="D196" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -10766,10 +10766,10 @@
         <v/>
       </c>
       <c r="K196" t="str">
-        <v>グリパンピンク</v>
+        <v>ゴールドスジエビ</v>
       </c>
       <c r="L196" t="str">
-        <v>4550133505539</v>
+        <v>4550133505829</v>
       </c>
       <c r="M196" t="str">
         <v/>
@@ -10789,16 +10789,16 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>DLD10809</v>
+        <v>DLD10838</v>
       </c>
       <c r="B197" t="str">
         <v>DL1067</v>
       </c>
       <c r="C197" t="str">
-        <v>ＢＨミニジグ１．３ｇ　テナガエビ</v>
+        <v>ＢＨミニジグ３．２ｇ　グリパンピンク</v>
       </c>
       <c r="D197" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -10819,10 +10819,10 @@
         <v/>
       </c>
       <c r="K197" t="str">
-        <v>テナガエビ</v>
+        <v>グリパンピンク</v>
       </c>
       <c r="L197" t="str">
-        <v>4550133505546</v>
+        <v>4550133505836</v>
       </c>
       <c r="M197" t="str">
         <v/>
@@ -10842,16 +10842,16 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>DLD10810</v>
+        <v>DLD10839</v>
       </c>
       <c r="B198" t="str">
         <v>DL1067</v>
       </c>
       <c r="C198" t="str">
-        <v>ＢＨミニジグ１．３ｇ　クリスタルシュリンプ</v>
+        <v>ＢＨミニジグ３．２ｇ　テナガエビ</v>
       </c>
       <c r="D198" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -10872,10 +10872,10 @@
         <v/>
       </c>
       <c r="K198" t="str">
-        <v>クリスタルシュリンプ</v>
+        <v>テナガエビ</v>
       </c>
       <c r="L198" t="str">
-        <v>4550133505553</v>
+        <v>4550133505843</v>
       </c>
       <c r="M198" t="str">
         <v/>
@@ -10895,16 +10895,16 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>DLD10811</v>
+        <v>DLD10840</v>
       </c>
       <c r="B199" t="str">
         <v>DL1067</v>
       </c>
       <c r="C199" t="str">
-        <v>ＢＨミニジグ１．３ｇ　ゴリ</v>
+        <v>ＢＨミニジグ３．２ｇ　クリスタルシュリンプ</v>
       </c>
       <c r="D199" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -10925,10 +10925,10 @@
         <v/>
       </c>
       <c r="K199" t="str">
-        <v>ゴリ</v>
+        <v>クリスタルシュリンプ</v>
       </c>
       <c r="L199" t="str">
-        <v>4550133505560</v>
+        <v>4550133505850</v>
       </c>
       <c r="M199" t="str">
         <v/>
@@ -10948,16 +10948,16 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>DLD10812</v>
+        <v>DLD10841</v>
       </c>
       <c r="B200" t="str">
         <v>DL1067</v>
       </c>
       <c r="C200" t="str">
-        <v>ＢＨミニジグ１．３ｇ　沼ザリ</v>
+        <v>ＢＨミニジグ３．２ｇ　ゴリ</v>
       </c>
       <c r="D200" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -10978,10 +10978,10 @@
         <v/>
       </c>
       <c r="K200" t="str">
-        <v>沼ザリ</v>
+        <v>ゴリ</v>
       </c>
       <c r="L200" t="str">
-        <v>4550133505577</v>
+        <v>4550133505867</v>
       </c>
       <c r="M200" t="str">
         <v/>
@@ -11001,16 +11001,16 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>DLD10813</v>
+        <v>DLD10842</v>
       </c>
       <c r="B201" t="str">
         <v>DL1067</v>
       </c>
       <c r="C201" t="str">
-        <v>ＢＨミニジグ１．３ｇ　スポーンシュリンプ</v>
+        <v>ＢＨミニジグ３．２ｇ　沼ザリ</v>
       </c>
       <c r="D201" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -11031,10 +11031,10 @@
         <v/>
       </c>
       <c r="K201" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>沼ザリ</v>
       </c>
       <c r="L201" t="str">
-        <v>4550133505584</v>
+        <v>4550133505874</v>
       </c>
       <c r="M201" t="str">
         <v/>
@@ -11054,16 +11054,16 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>DLD10814</v>
+        <v>DLD10843</v>
       </c>
       <c r="B202" t="str">
         <v>DL1067</v>
       </c>
       <c r="C202" t="str">
-        <v>ＢＨミニジグ１．３ｇ　ブラック</v>
+        <v>ＢＨミニジグ３．２ｇ　スポーンシュリンプ</v>
       </c>
       <c r="D202" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -11084,10 +11084,10 @@
         <v/>
       </c>
       <c r="K202" t="str">
-        <v>ブラック</v>
+        <v>スポーンシュリンプ</v>
       </c>
       <c r="L202" t="str">
-        <v>4550133505591</v>
+        <v>4550133505881</v>
       </c>
       <c r="M202" t="str">
         <v/>
@@ -11107,16 +11107,16 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>DLD10815</v>
+        <v>DLD10844</v>
       </c>
       <c r="B203" t="str">
         <v>DL1067</v>
       </c>
       <c r="C203" t="str">
-        <v>ＢＨミニジグ１．３ｇ　サマークロー</v>
+        <v>ＢＨミニジグ３．２ｇ　ブラック</v>
       </c>
       <c r="D203" t="str">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -11137,10 +11137,10 @@
         <v/>
       </c>
       <c r="K203" t="str">
-        <v>サマークロー</v>
+        <v>ブラック</v>
       </c>
       <c r="L203" t="str">
-        <v>4550133505607</v>
+        <v>4550133505898</v>
       </c>
       <c r="M203" t="str">
         <v/>
@@ -11160,16 +11160,16 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>DLD10816</v>
+        <v>DLD10845</v>
       </c>
       <c r="B204" t="str">
         <v>DL1067</v>
       </c>
       <c r="C204" t="str">
-        <v>ＢＨミニジグ１．８ｇ　グリーンパンプキン</v>
+        <v>ＢＨミニジグ３．２ｇ　サマークロー</v>
       </c>
       <c r="D204" t="str">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -11190,10 +11190,10 @@
         <v/>
       </c>
       <c r="K204" t="str">
-        <v>グリーンパンプキン</v>
+        <v>サマークロー</v>
       </c>
       <c r="L204" t="str">
-        <v>4550133505614</v>
+        <v>4550133505904</v>
       </c>
       <c r="M204" t="str">
         <v/>
@@ -11213,16 +11213,16 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>DLD10817</v>
+        <v>MLD11695</v>
       </c>
       <c r="B205" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C205" t="str">
-        <v>ＢＨミニジグ１．８ｇ　ゴールドスジエビ</v>
+        <v>MAGDRAFT HEAD ＃5/0 1/4oz.</v>
       </c>
       <c r="D205" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -11234,7 +11234,7 @@
         <v/>
       </c>
       <c r="H205" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -11243,10 +11243,10 @@
         <v/>
       </c>
       <c r="K205" t="str">
-        <v>ゴールドスジエビ</v>
+        <v>＃5/0 1/4oz.</v>
       </c>
       <c r="L205" t="str">
-        <v>4550133505621</v>
+        <v/>
       </c>
       <c r="M205" t="str">
         <v/>
@@ -11266,16 +11266,16 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>DLD10818</v>
+        <v>MLD11696</v>
       </c>
       <c r="B206" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C206" t="str">
-        <v>ＢＨミニジグ１．８ｇ　グリパンピンク</v>
+        <v>MAGDRAFT HEAD ＃5/0 3/8oz.</v>
       </c>
       <c r="D206" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -11287,7 +11287,7 @@
         <v/>
       </c>
       <c r="H206" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I206" t="str">
         <v/>
@@ -11296,10 +11296,10 @@
         <v/>
       </c>
       <c r="K206" t="str">
-        <v>グリパンピンク</v>
+        <v>＃5/0 3/8oz.</v>
       </c>
       <c r="L206" t="str">
-        <v>4550133505638</v>
+        <v/>
       </c>
       <c r="M206" t="str">
         <v/>
@@ -11319,16 +11319,16 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>DLD10819</v>
+        <v>MLD11697</v>
       </c>
       <c r="B207" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C207" t="str">
-        <v>ＢＨミニジグ１．８ｇ　テナガエビ</v>
+        <v>MAGDRAFT HEAD ＃5/0 1/2oz.</v>
       </c>
       <c r="D207" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E207" t="str">
         <v/>
@@ -11340,7 +11340,7 @@
         <v/>
       </c>
       <c r="H207" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I207" t="str">
         <v/>
@@ -11349,10 +11349,10 @@
         <v/>
       </c>
       <c r="K207" t="str">
-        <v>テナガエビ</v>
+        <v>＃5/0 1/2oz.</v>
       </c>
       <c r="L207" t="str">
-        <v>4550133505645</v>
+        <v/>
       </c>
       <c r="M207" t="str">
         <v/>
@@ -11372,16 +11372,16 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>DLD10820</v>
+        <v>MLD11698</v>
       </c>
       <c r="B208" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C208" t="str">
-        <v>ＢＨミニジグ１．８ｇ　クリスタルシュリンプ</v>
+        <v>MAGDRAFT HEAD ＃5/0 5/8oz.</v>
       </c>
       <c r="D208" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E208" t="str">
         <v/>
@@ -11393,7 +11393,7 @@
         <v/>
       </c>
       <c r="H208" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -11402,10 +11402,10 @@
         <v/>
       </c>
       <c r="K208" t="str">
-        <v>クリスタルシュリンプ</v>
+        <v>＃5/0 5/8oz.</v>
       </c>
       <c r="L208" t="str">
-        <v>4550133505652</v>
+        <v/>
       </c>
       <c r="M208" t="str">
         <v/>
@@ -11425,16 +11425,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>DLD10821</v>
+        <v>MLD11699</v>
       </c>
       <c r="B209" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C209" t="str">
-        <v>ＢＨミニジグ１．８ｇ　ゴリ</v>
+        <v>MAGDRAFT HEAD ＃5/0 3/4oz.</v>
       </c>
       <c r="D209" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E209" t="str">
         <v/>
@@ -11446,7 +11446,7 @@
         <v/>
       </c>
       <c r="H209" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I209" t="str">
         <v/>
@@ -11455,10 +11455,10 @@
         <v/>
       </c>
       <c r="K209" t="str">
-        <v>ゴリ</v>
+        <v>＃5/0 3/4oz.</v>
       </c>
       <c r="L209" t="str">
-        <v>4550133505669</v>
+        <v/>
       </c>
       <c r="M209" t="str">
         <v/>
@@ -11478,16 +11478,16 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>DLD10822</v>
+        <v>MLD11700</v>
       </c>
       <c r="B210" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C210" t="str">
-        <v>ＢＨミニジグ１．８ｇ　沼ザリ</v>
+        <v>MAGDRAFT HEAD ＃6/0 3/8oz.</v>
       </c>
       <c r="D210" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E210" t="str">
         <v/>
@@ -11499,7 +11499,7 @@
         <v/>
       </c>
       <c r="H210" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I210" t="str">
         <v/>
@@ -11508,10 +11508,10 @@
         <v/>
       </c>
       <c r="K210" t="str">
-        <v>沼ザリ</v>
+        <v>＃6/0 3/8oz.</v>
       </c>
       <c r="L210" t="str">
-        <v>4550133505676</v>
+        <v/>
       </c>
       <c r="M210" t="str">
         <v/>
@@ -11531,16 +11531,16 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>DLD10823</v>
+        <v>MLD11701</v>
       </c>
       <c r="B211" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C211" t="str">
-        <v>ＢＨミニジグ１．８ｇ　スポーンシュリンプ</v>
+        <v>MAGDRAFT HEAD ＃6/0 1/2oz.</v>
       </c>
       <c r="D211" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E211" t="str">
         <v/>
@@ -11552,7 +11552,7 @@
         <v/>
       </c>
       <c r="H211" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I211" t="str">
         <v/>
@@ -11561,10 +11561,10 @@
         <v/>
       </c>
       <c r="K211" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>＃6/0 1/2oz.</v>
       </c>
       <c r="L211" t="str">
-        <v>4550133505683</v>
+        <v/>
       </c>
       <c r="M211" t="str">
         <v/>
@@ -11584,16 +11584,16 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>DLD10824</v>
+        <v>MLD11702</v>
       </c>
       <c r="B212" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C212" t="str">
-        <v>ＢＨミニジグ１．８ｇ　ブラック</v>
+        <v>MAGDRAFT HEAD ＃6/0 5/8oz.</v>
       </c>
       <c r="D212" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E212" t="str">
         <v/>
@@ -11605,7 +11605,7 @@
         <v/>
       </c>
       <c r="H212" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I212" t="str">
         <v/>
@@ -11614,10 +11614,10 @@
         <v/>
       </c>
       <c r="K212" t="str">
-        <v>ブラック</v>
+        <v>＃6/0 5/8oz.</v>
       </c>
       <c r="L212" t="str">
-        <v>4550133505690</v>
+        <v/>
       </c>
       <c r="M212" t="str">
         <v/>
@@ -11637,16 +11637,16 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>DLD10825</v>
+        <v>MLD11703</v>
       </c>
       <c r="B213" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C213" t="str">
-        <v>ＢＨミニジグ１．８ｇ　サマークロー</v>
+        <v>MAGDRAFT HEAD ＃6/0 3/4oz.</v>
       </c>
       <c r="D213" t="str">
-        <v>1.8</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E213" t="str">
         <v/>
@@ -11658,7 +11658,7 @@
         <v/>
       </c>
       <c r="H213" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -11667,10 +11667,10 @@
         <v/>
       </c>
       <c r="K213" t="str">
-        <v>サマークロー</v>
+        <v>＃6/0 3/4oz.</v>
       </c>
       <c r="L213" t="str">
-        <v>4550133505706</v>
+        <v/>
       </c>
       <c r="M213" t="str">
         <v/>
@@ -11690,16 +11690,16 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>DLD10826</v>
+        <v>MLD11704</v>
       </c>
       <c r="B214" t="str">
-        <v>DL1067</v>
+        <v>ML1131</v>
       </c>
       <c r="C214" t="str">
-        <v>ＢＨミニジグ２．５ｇ　グリーンパンプキン</v>
+        <v>MAGDRAFT HEAD ＃6/0 1oz.</v>
       </c>
       <c r="D214" t="str">
-        <v>2.5</v>
+        <v>＃5/0：1/4oz.  3/8oz.  1/2oz.  5/8oz.  3/4oz.＃6/0： 3/8oz.  1/2oz.  5/8oz.  3/4oz.  1oz.</v>
       </c>
       <c r="E214" t="str">
         <v/>
@@ -11711,7 +11711,7 @@
         <v/>
       </c>
       <c r="H214" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）＃5/01/4oz. : 850円3/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円＃6/03/8oz. : 860円1/2oz. : 870円5/8oz. : 880円3/4oz. : 890円1oz. : 900 円</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -11720,10 +11720,10 @@
         <v/>
       </c>
       <c r="K214" t="str">
-        <v>グリーンパンプキン</v>
+        <v>＃6/0 1oz.</v>
       </c>
       <c r="L214" t="str">
-        <v>4550133505713</v>
+        <v/>
       </c>
       <c r="M214" t="str">
         <v/>
@@ -11743,16 +11743,16 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>DLD10827</v>
+        <v>MLD11715</v>
       </c>
       <c r="B215" t="str">
-        <v>DL1067</v>
+        <v>ML1133</v>
       </c>
       <c r="C215" t="str">
-        <v>ＢＨミニジグ２．５ｇ　ゴールドスジエビ</v>
+        <v>OKASHIRA SCREW HEAD</v>
       </c>
       <c r="D215" t="str">
-        <v>2.5</v>
+        <v>＃2/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃3/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃4/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.</v>
       </c>
       <c r="E215" t="str">
         <v/>
@@ -11764,7 +11764,7 @@
         <v/>
       </c>
       <c r="H215" t="str">
-        <v>500</v>
+        <v/>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -11773,10 +11773,10 @@
         <v/>
       </c>
       <c r="K215" t="str">
-        <v>ゴールドスジエビ</v>
+        <v/>
       </c>
       <c r="L215" t="str">
-        <v>4550133505720</v>
+        <v/>
       </c>
       <c r="M215" t="str">
         <v/>
@@ -11796,16 +11796,16 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>DLD10828</v>
+        <v>MLD11716</v>
       </c>
       <c r="B216" t="str">
-        <v>DL1067</v>
+        <v>ML1134</v>
       </c>
       <c r="C216" t="str">
-        <v>ＢＨミニジグ２．５ｇ　グリパンピンク</v>
+        <v>OKASHIRA HEAD</v>
       </c>
       <c r="D216" t="str">
-        <v>2.5</v>
+        <v>＃2/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃3/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.＃4/0：1/16oz., 1/8oz., 3/16oz., 1/4oz.</v>
       </c>
       <c r="E216" t="str">
         <v/>
@@ -11817,7 +11817,7 @@
         <v/>
       </c>
       <c r="H216" t="str">
-        <v>500</v>
+        <v/>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -11826,10 +11826,10 @@
         <v/>
       </c>
       <c r="K216" t="str">
-        <v>グリパンピンク</v>
+        <v/>
       </c>
       <c r="L216" t="str">
-        <v>4550133505737</v>
+        <v/>
       </c>
       <c r="M216" t="str">
         <v/>
@@ -11849,16 +11849,16 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>DLD10829</v>
+        <v>MLD11717</v>
       </c>
       <c r="B217" t="str">
-        <v>DL1067</v>
+        <v>ML1135</v>
       </c>
       <c r="C217" t="str">
-        <v>ＢＨミニジグ２．５ｇ　テナガエビ</v>
+        <v>OKASHIRA HEAD-HG（Huge-Contact）</v>
       </c>
       <c r="D217" t="str">
-        <v>2.5</v>
+        <v>＃2/0：3/8oz., 1/2oz., 5/8oz.＃3/0：3/8oz., 1/2oz., 5/8oz.＃4/0：1/2oz., 3/8oz., 3/4oz.＃5/0：1/2oz., 3/8oz., 3/4oz.</v>
       </c>
       <c r="E217" t="str">
         <v/>
@@ -11870,7 +11870,7 @@
         <v/>
       </c>
       <c r="H217" t="str">
-        <v>500</v>
+        <v/>
       </c>
       <c r="I217" t="str">
         <v/>
@@ -11879,10 +11879,10 @@
         <v/>
       </c>
       <c r="K217" t="str">
-        <v>テナガエビ</v>
+        <v/>
       </c>
       <c r="L217" t="str">
-        <v>4550133505744</v>
+        <v/>
       </c>
       <c r="M217" t="str">
         <v/>
@@ -11902,16 +11902,16 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>DLD10830</v>
+        <v>MLD11718</v>
       </c>
       <c r="B218" t="str">
-        <v>DL1067</v>
+        <v>ML1136</v>
       </c>
       <c r="C218" t="str">
-        <v>ＢＨミニジグ２．５ｇ　クリスタルシュリンプ</v>
+        <v>ROBIN BLADE B BLUE</v>
       </c>
       <c r="D218" t="str">
-        <v>2.5</v>
+        <v>3/8oz.</v>
       </c>
       <c r="E218" t="str">
         <v/>
@@ -11923,7 +11923,7 @@
         <v/>
       </c>
       <c r="H218" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）1,150 円</v>
       </c>
       <c r="I218" t="str">
         <v/>
@@ -11932,10 +11932,10 @@
         <v/>
       </c>
       <c r="K218" t="str">
-        <v>クリスタルシュリンプ</v>
+        <v>B BLUE</v>
       </c>
       <c r="L218" t="str">
-        <v>4550133505751</v>
+        <v/>
       </c>
       <c r="M218" t="str">
         <v/>
@@ -11955,16 +11955,16 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>DLD10831</v>
+        <v>MLD11719</v>
       </c>
       <c r="B219" t="str">
-        <v>DL1067</v>
+        <v>ML1136</v>
       </c>
       <c r="C219" t="str">
-        <v>ＢＨミニジグ２．５ｇ　ゴリ</v>
+        <v>ROBIN BLADE VARRACUDA HASU</v>
       </c>
       <c r="D219" t="str">
-        <v>2.5</v>
+        <v>3/8oz.</v>
       </c>
       <c r="E219" t="str">
         <v/>
@@ -11976,7 +11976,7 @@
         <v/>
       </c>
       <c r="H219" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）1,150 円</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -11985,10 +11985,10 @@
         <v/>
       </c>
       <c r="K219" t="str">
-        <v>ゴリ</v>
+        <v>VARRACUDA HASU</v>
       </c>
       <c r="L219" t="str">
-        <v>4550133505768</v>
+        <v/>
       </c>
       <c r="M219" t="str">
         <v/>
@@ -12008,16 +12008,16 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>DLD10832</v>
+        <v>MLD11720</v>
       </c>
       <c r="B220" t="str">
-        <v>DL1067</v>
+        <v>ML1136</v>
       </c>
       <c r="C220" t="str">
-        <v>ＢＨミニジグ２．５ｇ　沼ザリ</v>
+        <v>ROBIN BLADE TOWER BLIDGE WAKASAGI</v>
       </c>
       <c r="D220" t="str">
-        <v>2.5</v>
+        <v>3/8oz.</v>
       </c>
       <c r="E220" t="str">
         <v/>
@@ -12029,7 +12029,7 @@
         <v/>
       </c>
       <c r="H220" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）1,150 円</v>
       </c>
       <c r="I220" t="str">
         <v/>
@@ -12038,10 +12038,10 @@
         <v/>
       </c>
       <c r="K220" t="str">
-        <v>沼ザリ</v>
+        <v>TOWER BLIDGE WAKASAGI</v>
       </c>
       <c r="L220" t="str">
-        <v>4550133505775</v>
+        <v/>
       </c>
       <c r="M220" t="str">
         <v/>
@@ -12061,16 +12061,16 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>DLD10833</v>
+        <v>MLD11721</v>
       </c>
       <c r="B221" t="str">
-        <v>DL1067</v>
+        <v>ML1136</v>
       </c>
       <c r="C221" t="str">
-        <v>ＢＨミニジグ２．５ｇ　スポーンシュリンプ</v>
+        <v>ROBIN BLADE WARS GILL</v>
       </c>
       <c r="D221" t="str">
-        <v>2.5</v>
+        <v>3/8oz.</v>
       </c>
       <c r="E221" t="str">
         <v/>
@@ -12082,7 +12082,7 @@
         <v/>
       </c>
       <c r="H221" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）1,150 円</v>
       </c>
       <c r="I221" t="str">
         <v/>
@@ -12091,10 +12091,10 @@
         <v/>
       </c>
       <c r="K221" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>WARS GILL</v>
       </c>
       <c r="L221" t="str">
-        <v>4550133505782</v>
+        <v/>
       </c>
       <c r="M221" t="str">
         <v/>
@@ -12114,16 +12114,16 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>DLD10834</v>
+        <v>MLD11722</v>
       </c>
       <c r="B222" t="str">
-        <v>DL1067</v>
+        <v>ML1136</v>
       </c>
       <c r="C222" t="str">
-        <v>ＢＨミニジグ２．５ｇ　ブラック</v>
+        <v>ROBIN BLADE ANOARO GILL</v>
       </c>
       <c r="D222" t="str">
-        <v>2.5</v>
+        <v>3/8oz.</v>
       </c>
       <c r="E222" t="str">
         <v/>
@@ -12135,7 +12135,7 @@
         <v/>
       </c>
       <c r="H222" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）1,150 円</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -12144,10 +12144,10 @@
         <v/>
       </c>
       <c r="K222" t="str">
-        <v>ブラック</v>
+        <v>ANOARO GILL</v>
       </c>
       <c r="L222" t="str">
-        <v>4550133505799</v>
+        <v/>
       </c>
       <c r="M222" t="str">
         <v/>
@@ -12167,16 +12167,16 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>DLD10835</v>
+        <v>MLD11723</v>
       </c>
       <c r="B223" t="str">
-        <v>DL1067</v>
+        <v>ML1136</v>
       </c>
       <c r="C223" t="str">
-        <v>ＢＨミニジグ２．５ｇ　サマークロー</v>
+        <v>ROBIN BLADE CHART DRIVER</v>
       </c>
       <c r="D223" t="str">
-        <v>2.5</v>
+        <v>3/8oz.</v>
       </c>
       <c r="E223" t="str">
         <v/>
@@ -12188,7 +12188,7 @@
         <v/>
       </c>
       <c r="H223" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）1,150 円</v>
       </c>
       <c r="I223" t="str">
         <v/>
@@ -12197,10 +12197,10 @@
         <v/>
       </c>
       <c r="K223" t="str">
-        <v>サマークロー</v>
+        <v>CHART DRIVER</v>
       </c>
       <c r="L223" t="str">
-        <v>4550133505805</v>
+        <v/>
       </c>
       <c r="M223" t="str">
         <v/>
@@ -12220,16 +12220,16 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>DLD10836</v>
+        <v>MLD11734</v>
       </c>
       <c r="B224" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C224" t="str">
-        <v>ＢＨミニジグ３．２ｇ　グリーンパンプキン</v>
+        <v>UOZE SWIMMER HASU</v>
       </c>
       <c r="D224" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E224" t="str">
         <v/>
@@ -12241,7 +12241,7 @@
         <v/>
       </c>
       <c r="H224" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -12250,13 +12250,13 @@
         <v/>
       </c>
       <c r="K224" t="str">
-        <v>グリーンパンプキン</v>
+        <v>HASU</v>
       </c>
       <c r="L224" t="str">
-        <v>4550133505812</v>
+        <v/>
       </c>
       <c r="M224" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N224" t="str">
         <v/>
@@ -12273,16 +12273,16 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>DLD10837</v>
+        <v>MLD11735</v>
       </c>
       <c r="B225" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C225" t="str">
-        <v>ＢＨミニジグ３．２ｇ　ゴールドスジエビ</v>
+        <v>UOZE SWIMMER AYU</v>
       </c>
       <c r="D225" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E225" t="str">
         <v/>
@@ -12294,7 +12294,7 @@
         <v/>
       </c>
       <c r="H225" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I225" t="str">
         <v/>
@@ -12303,13 +12303,13 @@
         <v/>
       </c>
       <c r="K225" t="str">
-        <v>ゴールドスジエビ</v>
+        <v>AYU</v>
       </c>
       <c r="L225" t="str">
-        <v>4550133505829</v>
+        <v/>
       </c>
       <c r="M225" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N225" t="str">
         <v/>
@@ -12326,16 +12326,16 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>DLD10838</v>
+        <v>MLD11736</v>
       </c>
       <c r="B226" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C226" t="str">
-        <v>ＢＨミニジグ３．２ｇ　グリパンピンク</v>
+        <v>UOZE SWIMMER WAKASAGI</v>
       </c>
       <c r="D226" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E226" t="str">
         <v/>
@@ -12347,7 +12347,7 @@
         <v/>
       </c>
       <c r="H226" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I226" t="str">
         <v/>
@@ -12356,13 +12356,13 @@
         <v/>
       </c>
       <c r="K226" t="str">
-        <v>グリパンピンク</v>
+        <v>WAKASAGI</v>
       </c>
       <c r="L226" t="str">
-        <v>4550133505836</v>
+        <v/>
       </c>
       <c r="M226" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N226" t="str">
         <v/>
@@ -12379,16 +12379,16 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>DLD10839</v>
+        <v>MLD11737</v>
       </c>
       <c r="B227" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C227" t="str">
-        <v>ＢＨミニジグ３．２ｇ　テナガエビ</v>
+        <v>UOZE SWIMMER GILL</v>
       </c>
       <c r="D227" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E227" t="str">
         <v/>
@@ -12400,7 +12400,7 @@
         <v/>
       </c>
       <c r="H227" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -12409,13 +12409,13 @@
         <v/>
       </c>
       <c r="K227" t="str">
-        <v>テナガエビ</v>
+        <v>GILL</v>
       </c>
       <c r="L227" t="str">
-        <v>4550133505843</v>
+        <v/>
       </c>
       <c r="M227" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N227" t="str">
         <v/>
@@ -12432,16 +12432,16 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>DLD10840</v>
+        <v>MLD11738</v>
       </c>
       <c r="B228" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C228" t="str">
-        <v>ＢＨミニジグ３．２ｇ　クリスタルシュリンプ</v>
+        <v>UOZE SWIMMER SMOKE SHAD</v>
       </c>
       <c r="D228" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E228" t="str">
         <v/>
@@ -12453,7 +12453,7 @@
         <v/>
       </c>
       <c r="H228" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I228" t="str">
         <v/>
@@ -12462,13 +12462,13 @@
         <v/>
       </c>
       <c r="K228" t="str">
-        <v>クリスタルシュリンプ</v>
+        <v>SMOKE SHAD</v>
       </c>
       <c r="L228" t="str">
-        <v>4550133505850</v>
+        <v/>
       </c>
       <c r="M228" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N228" t="str">
         <v/>
@@ -12485,16 +12485,16 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>DLD10841</v>
+        <v>MLD11739</v>
       </c>
       <c r="B229" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C229" t="str">
-        <v>ＢＨミニジグ３．２ｇ　ゴリ</v>
+        <v>UOZE SWIMMER GOLDEN SHINER</v>
       </c>
       <c r="D229" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E229" t="str">
         <v/>
@@ -12506,7 +12506,7 @@
         <v/>
       </c>
       <c r="H229" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -12515,13 +12515,13 @@
         <v/>
       </c>
       <c r="K229" t="str">
-        <v>ゴリ</v>
+        <v>GOLDEN SHINER</v>
       </c>
       <c r="L229" t="str">
-        <v>4550133505867</v>
+        <v/>
       </c>
       <c r="M229" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N229" t="str">
         <v/>
@@ -12538,16 +12538,16 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>DLD10842</v>
+        <v>MLD11740</v>
       </c>
       <c r="B230" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C230" t="str">
-        <v>ＢＨミニジグ３．２ｇ　沼ザリ</v>
+        <v>UOZE SWIMMER GURIPAN</v>
       </c>
       <c r="D230" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E230" t="str">
         <v/>
@@ -12559,7 +12559,7 @@
         <v/>
       </c>
       <c r="H230" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -12568,13 +12568,13 @@
         <v/>
       </c>
       <c r="K230" t="str">
-        <v>沼ザリ</v>
+        <v>GURIPAN</v>
       </c>
       <c r="L230" t="str">
-        <v>4550133505874</v>
+        <v/>
       </c>
       <c r="M230" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N230" t="str">
         <v/>
@@ -12591,16 +12591,16 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>DLD10843</v>
+        <v>MLD11741</v>
       </c>
       <c r="B231" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C231" t="str">
-        <v>ＢＨミニジグ３．２ｇ　スポーンシュリンプ</v>
+        <v>UOZE SWIMMER BLACK BLUE</v>
       </c>
       <c r="D231" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E231" t="str">
         <v/>
@@ -12612,7 +12612,7 @@
         <v/>
       </c>
       <c r="H231" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -12621,13 +12621,13 @@
         <v/>
       </c>
       <c r="K231" t="str">
-        <v>スポーンシュリンプ</v>
+        <v>BLACK BLUE</v>
       </c>
       <c r="L231" t="str">
-        <v>4550133505881</v>
+        <v/>
       </c>
       <c r="M231" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N231" t="str">
         <v/>
@@ -12644,16 +12644,16 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>DLD10844</v>
+        <v>MLD11742</v>
       </c>
       <c r="B232" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C232" t="str">
-        <v>ＢＨミニジグ３．２ｇ　ブラック</v>
+        <v>UOZE SWIMMER SEXY SHAD</v>
       </c>
       <c r="D232" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E232" t="str">
         <v/>
@@ -12665,7 +12665,7 @@
         <v/>
       </c>
       <c r="H232" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -12674,13 +12674,13 @@
         <v/>
       </c>
       <c r="K232" t="str">
-        <v>ブラック</v>
+        <v>SEXY SHAD</v>
       </c>
       <c r="L232" t="str">
-        <v>4550133505898</v>
+        <v/>
       </c>
       <c r="M232" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N232" t="str">
         <v/>
@@ -12697,16 +12697,16 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>DLD10845</v>
+        <v>MLD11743</v>
       </c>
       <c r="B233" t="str">
-        <v>DL1067</v>
+        <v>ML1138</v>
       </c>
       <c r="C233" t="str">
-        <v>ＢＨミニジグ３．２ｇ　サマークロー</v>
+        <v>UOZE SWIMMER REACTION CHART</v>
       </c>
       <c r="D233" t="str">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="E233" t="str">
         <v/>
@@ -12718,7 +12718,7 @@
         <v/>
       </c>
       <c r="H233" t="str">
-        <v>500</v>
+        <v>メーカー希望小売価格（税別）3/16oz. : 1,020 円1/4oz. : 1,050 円3/8oz. : 1,080 円1/2oz. : 1,110 円5/8oz. : 1,140 円3/4oz. : 1,170 円</v>
       </c>
       <c r="I233" t="str">
         <v/>
@@ -12727,13 +12727,13 @@
         <v/>
       </c>
       <c r="K233" t="str">
-        <v>サマークロー</v>
+        <v>REACTION CHART</v>
       </c>
       <c r="L233" t="str">
-        <v>4550133505904</v>
+        <v/>
       </c>
       <c r="M233" t="str">
-        <v/>
+        <v>3/16oz. (Hook : #3/0)1/4oz. (Hook : #4/0)3/8oz. (Hook : #4/0)1/2oz. (Hook : #4/0)5/8oz. (Hook : #5/0)3/4oz. (Hook : #5/0)</v>
       </c>
       <c r="N233" t="str">
         <v/>
